--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -674,14 +674,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36 Surrey 3 512 km 52 160 km SEL S-AWC PANOROOF NAVIGATION 360 CAMERA SEL S-AWC PANOROOF ADAPTIVE CRUISE CONTROL MULTI-VIEW CAMERA SYSTEM 20 ALLOY WHEELS BLIND SPOT WARNING LANE DEPARTURE WARNING REAR CROSS TRAFFIC ALERT 3-ZONE AUTOMATIC CLIMATE CONTROL HEATED LEATHER SEATS STEERING WHEEL NAVIGATION POWER LIFTGATE KEY Payment Calculator Trade-</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33872</v>
+        <v>33995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52160</v>
+        <v>50530</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -691,12 +691,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, Leather, Navigation, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -719,16 +719,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
+        <v>34492</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -736,12 +740,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -756,7 +760,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -764,14 +768,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34492</v>
+        <v>34995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42233</v>
+        <v>51023</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -785,7 +789,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof, AWD, Certified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -805,7 +809,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -813,18 +817,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34995</v>
+          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
+        </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>51023</v>
+        <v>37063</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -834,7 +835,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -854,19 +855,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26 Surrey 3 526 km 31 070 km GT LEATHER NAVI PANO SUNROOF SXM REAR VIEW CAM Drive away today this GT S-AWC featuring HEATED FRONT SEATS POWER DUAL-PANE SUNROOF BACK-UP CAMERA BLIND-SPOT REAR CROSS PATH DETECTION POWER DRIVER SEAT a c with dual zone temperature control cruise control a leather wrapped ste Trade-</t>
+          <t>19 North Vancouver 3 538 km 15 549 km GT Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>31070</v>
+        <v>15549</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, Leather, Heated Seats, AWD, Backup Cam</t>
+          <t>Sunroof, Certified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -896,7 +897,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -904,30 +905,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>37063</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+          <t>Used</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -936,39 +922,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -981,7 +936,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -855,34 +855,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19 North Vancouver 3 538 km 15 549 km GT Trade- Certified Pre-Owned</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>15549</v>
+          <t>Used</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof, Certified</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -891,39 +880,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:K11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -935,7 +893,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -855,33 +855,75 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV GT</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>19 North Vancouver 3 538 km 15 549 km GT Trade- Certified Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>15549</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof, Certified</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2023 Mitsubishi Outlander PHEV Used</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -893,6 +935,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -644,14 +644,14 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34492</v>
+        <v>33995</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -666,37 +666,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>50530</v>
+        <v>34492</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -711,7 +695,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -719,20 +703,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34492</v>
+        <v>33995</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>50530</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -740,12 +720,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -760,7 +740,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -768,14 +748,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
+          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34995</v>
+        <v>34492</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>51023</v>
+        <v>42233</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -789,7 +769,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, AWD, Certified</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -809,25 +789,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
-        </is>
+          <t>le awd 7 places toit ouvrant panoramique gps</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>35473</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>37063</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -835,12 +814,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -855,21 +834,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19 North Vancouver 3 538 km 15 549 km GT Trade- Certified Pre-Owned</t>
-        </is>
+          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34995</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>15549</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>51023</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -877,7 +863,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, Certified</t>
+          <t>Sunroof, AWD, Certified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -897,7 +883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -905,25 +891,71 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>37063</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:K13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -936,6 +968,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,21 +608,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33992</v>
+        <v>34998</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -644,14 +644,14 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33995</v>
+        <v>33992</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -673,14 +673,14 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34492</v>
+        <v>33995</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -695,37 +695,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>34492</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -740,7 +724,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -748,20 +732,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34492</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>50530</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -769,12 +749,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -789,24 +769,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>le awd 7 places toit ouvrant panoramique gps</t>
+          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35473</v>
+        <v>34492</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -814,12 +798,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -834,28 +818,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
+          <t>le awd 7 places toit ouvrant panoramique gps</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34995</v>
+        <v>35473</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>51023</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -863,12 +843,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, AWD, Certified</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -883,7 +863,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -891,15 +871,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
-        </is>
+          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34995</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37063</v>
+        <v>51023</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -909,7 +892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD, Certified</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -929,7 +912,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -937,25 +920,71 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>37063</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -969,6 +998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,8 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +507,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Days Tracked</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Listing</t>
         </is>
       </c>
@@ -538,7 +544,7 @@
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -567,7 +573,7 @@
           <t>Blainville Mitsubishi</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -596,7 +602,7 @@
           <t>Blainville Mitsubishi</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -625,7 +631,7 @@
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -654,7 +660,7 @@
           <t>Blainville Mitsubishi</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -683,7 +689,7 @@
           <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -712,7 +718,7 @@
           <t>Blainville Mitsubishi</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -757,7 +763,7 @@
           <t>Otogo.ca</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -806,7 +812,7 @@
           <t>AutoTrader</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -851,7 +857,7 @@
           <t>Otogo.ca</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -900,7 +906,7 @@
           <t>AutoTrader</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -912,7 +918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -920,85 +926,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30 North Bay 304 km 37 063 km GT Proudly Serving North Bay Surrounding Area For 15 Years We Offer The Best Customer Service Around And We Take Pride Always Going The Extra Mile For Our Customers When You Purchase A Vehicle From Top Picks We Guarantee Customer Satisfaction All Of Our Vehicles Are Trade- Reserve online</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>37063</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+          <t>Used</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:L13"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -592,7 +592,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32992</v>
+        <v>32892</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -708,7 +708,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34492</v>
+        <v>34441</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34492</v>
+        <v>34441</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>42233</v>
@@ -877,11 +877,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36 Brossard 174 km 51 023 km LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NAVIG LE-S AWC Syst me hybride rechargeable Moteur essence 2 4 L Double moteur lectrique avant et arri re Super All-Wheel Control S-AWC Transmission automatique Jantes en alliage Si ges avant chauffants Volant chauffant Climatisation automa Trade- Certified Pre-Owned</t>
+          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>51023</v>
@@ -898,13 +898,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
-        </is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -544,6 +544,9 @@
           <t>Kijiji</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
@@ -570,8 +573,11 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
-        </is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -599,8 +605,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
-        </is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -631,6 +640,9 @@
           <t>Hondasoreltracy</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
@@ -657,8 +669,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
-        </is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -689,6 +704,9 @@
           <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
@@ -715,8 +733,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi</t>
-        </is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -760,8 +781,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
-        </is>
+          <t>Otogo.ca, Toyotamontlaurier</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -809,8 +833,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
-        </is>
+          <t>AutoTrader, Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -857,6 +884,9 @@
           <t>Otogo.ca</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
@@ -903,7 +933,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -939,6 +969,9 @@
         <is>
           <t>Lefebvre Toyota</t>
         </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -959,15 +959,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Used</t>
-        </is>
+          <t>3 Vancouver 3 536 km 49 174 km SEL S-AWC Trade-</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>49174</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -979,8 +990,91 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sunroof, Backup Cam</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Used</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -994,6 +1088,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
   </definedNames>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -522,30 +522,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5000 cash incentive Lease Takeover</t>
-        </is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>41000</v>
+        <v>31992</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -566,7 +561,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31992</v>
+        <v>32892</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -577,7 +572,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -591,25 +586,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32892</v>
+        <v>34998</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -623,25 +618,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34998</v>
+        <v>33992</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -662,18 +657,18 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33992</v>
+        <v>33995</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -694,18 +689,18 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33995</v>
+        <v>34441</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -719,25 +714,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -751,7 +762,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -759,16 +770,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>34441</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -776,16 +791,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -799,28 +814,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>le awd 7 places toit ouvrant panoramique gps</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34441</v>
+        <v>35473</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -828,16 +839,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -851,24 +862,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>le awd 7 places toit ouvrant panoramique gps</t>
+          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>35473</v>
+        <v>33995</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>51023</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -876,16 +891,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, AutoTrader</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -899,7 +914,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -907,18 +922,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>33995</v>
+          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
+        </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>51023</v>
+        <v>47980</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -928,12 +940,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, Backup Cam</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -951,7 +963,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -959,30 +971,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3 Vancouver 3 536 km 49 174 km SEL S-AWC Trade-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>49174</v>
+          <t>Used</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -990,91 +991,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Sunroof, Backup Cam</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1088,8 +1006,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Results" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lease Takeovers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dealers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -452,6 +454,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,6 +518,11 @@
           <t>Listing</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Price History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -522,21 +530,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2023</v>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5000 cash incentive Lease Takeover</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31992</v>
+        <v>5000</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>41000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -547,6 +560,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -561,7 +575,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32892</v>
+        <v>31992</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -579,6 +593,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -586,21 +601,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34998</v>
+        <v>32892</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -611,6 +626,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -618,21 +634,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33992</v>
+        <v>34998</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -643,6 +659,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -657,14 +674,14 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33995</v>
+        <v>33992</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -675,6 +692,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -689,14 +707,14 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -707,6 +725,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -714,37 +733,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>34441</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -755,6 +758,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -762,7 +766,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -770,20 +774,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>50530</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -791,12 +791,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -807,6 +807,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -814,24 +815,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>le awd 7 places toit ouvrant panoramique gps</t>
+          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35473</v>
+        <v>34441</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -839,12 +844,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -855,6 +860,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -862,28 +868,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
+          <t>le awd 7 places toit ouvrant panoramique gps</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33995</v>
+        <v>35473</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>51023</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -891,12 +893,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -907,6 +909,7 @@
           <t>View</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -914,7 +917,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -922,15 +925,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
-        </is>
+          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>33995</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>47980</v>
+        <v>51023</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -940,22 +946,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof, Backup Cam</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -963,7 +970,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -971,28 +978,79 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sunroof, Backup Cam</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV Used</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1006,6 +1064,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5059,4 +5118,108 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vehicle</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trim</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Last Price ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mileage (km)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Days on Market</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Removed (days ago)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>First Seen</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Last Seen</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Price History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No tracked listing has been removed/sold in the last 21 days.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -533,11 +533,6 @@
           <t>Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5000 cash incentive Lease Takeover</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="n">
         <v>5000</v>
       </c>
@@ -553,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -586,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -619,7 +614,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -652,7 +647,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -685,7 +680,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -707,18 +702,18 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33995</v>
+        <v>34441</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -733,25 +728,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -766,7 +777,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -774,16 +785,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>34441</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -791,16 +806,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -815,7 +830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -823,14 +838,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22 Mirabel 136 km 42 233 km LE S-AWC SU DE ET CUIR VOLANT CHAUFFANT GROUPE LECTRIQUE BOUTON POUSSOIR ENTR E SANS CL FAST-KEY BLUETOOTH COMMANDE VOCALE AU VOLANT APPLE CARPLAY ANDROID AUTO SI GES AVANT CHAUFFANTS VOLANT CHAUFFANT INT RIEUR EN SIMILICUIR SI GE CONDUCTEUR LECTRIQUE CLIMATISATION AUTOMATIQUE TRI-ZONE CAM Payment Calculator Trade- Certified Pre-Owned</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>42233</v>
+        <v>51023</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -844,16 +859,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -868,41 +883,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2024</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>le awd 7 places toit ouvrant panoramique gps</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>35473</v>
-      </c>
       <c r="F11" s="2" t="n">
-        <v>56845</v>
+        <v>60230</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Certified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -917,26 +920,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2023</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LE CUIR TOIT PANO CRUISE CONTROL CAM RECUL NA</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>33995</v>
-      </c>
       <c r="F12" s="2" t="n">
-        <v>51023</v>
+        <v>47980</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -946,12 +941,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, Backup Cam</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -976,36 +971,16 @@
       <c r="C13" t="n">
         <v>2023</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2 Scarborough 345 km 47 980 km Auto sunroof blue tooth blind spot rear camera Upfront Pricing No Haggling No Hassles We offer our best price upfront for a transparent and stress-free car buying experience Safety Guaranteed All vehicles exceed Ontario safety standards through our comprehensive reconditioning process Family-Friendly Focus We ll h Trade-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sunroof, Backup Cam</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1014,43 +989,8 @@
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV Used</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1064,7 +1004,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5126,7 +5065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5214,12 +5153,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No tracked listing has been removed/sold in the last 21 days.</t>
-        </is>
-      </c>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>35473</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>56845</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:M3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -883,29 +883,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>60230</v>
+        <v>2023</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Certified</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -914,83 +907,8 @@
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Sunroof, Backup Cam</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1002,8 +920,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5065,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5153,27 +5069,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>35473</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -5184,12 +5097,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5202,50 +5115,143 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="n">
-        <v>33995</v>
+      <c r="E3" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>35473</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>56845</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M3"/>
+  <autoFilter ref="A1:M5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$5</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -662,32 +662,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33992</v>
+        <v>32911</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>56845</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -702,7 +722,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34441</v>
+        <v>33992</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -713,7 +733,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -728,41 +748,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>34441</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -777,7 +781,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -785,20 +789,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>50530</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -806,16 +806,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, AWD, Certified</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -838,20 +838,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33995</v>
+        <v>34441</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>51023</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>42233</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -859,16 +855,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -883,32 +879,122 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>51023</v>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>66091</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -920,6 +1006,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5069,40 +5157,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E2" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5115,31 +5210,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5157,43 +5256,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2024</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>35473</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>56845</v>
+        <v>60230</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5226,7 +5318,7 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,25 +563,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31992</v>
+        <v>32995</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>37000</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -603,7 +619,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32892</v>
+        <v>31992</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -614,7 +630,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -629,25 +645,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34998</v>
+        <v>32892</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -662,52 +678,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2024</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>56845</v>
+        <v>34998</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -733,7 +729,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -766,7 +762,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -815,7 +811,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -864,7 +860,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -913,7 +909,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -928,33 +924,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2023</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>66091</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -963,38 +948,8 @@
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1007,7 +962,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5069,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5157,35 +5111,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -5197,7 +5147,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5205,45 +5155,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>34995</v>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>66091</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5256,36 +5213,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E4" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5305,13 +5273,17 @@
         <v>2023</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5322,28 +5294,114 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="E6" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,48 +563,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32995</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>37000</v>
+        <v>30992</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -619,7 +607,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31992</v>
+        <v>32892</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -630,7 +618,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -645,25 +633,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32892</v>
+        <v>34998</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -678,25 +666,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>33492</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -729,7 +717,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -744,25 +732,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>34441</v>
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -777,41 +781,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>50530</v>
+        <v>34992</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -826,7 +814,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -834,14 +822,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34441</v>
+        <v>35025</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>42233</v>
+        <v>45016</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -851,16 +839,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -905,11 +893,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Otogo.ca, Kijiji</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -924,32 +912,130 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2023</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34699</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>64022</v>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>34985</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>60543</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -962,6 +1048,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5023,7 +5111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5111,31 +5199,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>56845</v>
+        <v>34441</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -5147,7 +5228,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5155,16 +5236,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5172,23 +5249,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34995</v>
+        <v>34441</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>66091</v>
+        <v>42233</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -5200,7 +5277,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5213,11 +5290,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5225,35 +5302,31 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34441</v>
+        <v>32995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>37000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5266,40 +5339,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>32911</v>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5307,20 +5383,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>34995</v>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>60230</v>
+        <v>66091</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5332,16 +5419,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5354,47 +5441,188 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
+        <v>34441</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>42233</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AutoTrader, Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="E8" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="E9" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
         <v>33995</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5402,6 +5630,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -822,14 +822,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35025</v>
+        <v>33995</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45016</v>
+        <v>51023</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -844,11 +844,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -871,14 +871,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -888,16 +888,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -942,11 +942,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34985</v>
+        <v>35005</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>60543</v>
+        <v>67282</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -986,23 +986,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1025,7 +1029,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -5219,7 +5223,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5268,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5317,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5366,7 +5370,7 @@
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5419,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5472,7 +5476,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5518,7 +5522,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5560,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5602,7 +5606,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -600,25 +600,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32892</v>
+        <v>32995</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>37000</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -633,25 +649,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34998</v>
+        <v>32892</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -666,25 +682,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33492</v>
+        <v>34998</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -706,7 +722,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33992</v>
+        <v>33492</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -717,7 +733,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -732,41 +748,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>33992</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -781,25 +781,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n">
-        <v>34992</v>
+        <v>33995</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -814,7 +830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -822,14 +838,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33995</v>
+        <v>35005</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>51023</v>
+        <v>36197</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -844,18 +860,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -863,41 +883,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -912,7 +916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -920,14 +924,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34985</v>
+        <v>33995</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>60543</v>
+        <v>51023</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -937,16 +941,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -973,10 +977,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35005</v>
+        <v>34699</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>67282</v>
+        <v>64022</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -986,27 +990,23 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1014,32 +1014,81 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2023</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>34985</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>60543</v>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="K15" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1054,6 +1103,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5115,7 +5165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5223,7 +5273,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5272,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5294,7 +5344,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5302,35 +5352,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32995</v>
+        <v>32911</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37000</v>
+        <v>56845</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5338,43 +5388,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32911</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56845</v>
+        <v>66091</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5387,16 +5441,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5404,35 +5454,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>34441</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>66091</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5445,47 +5499,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>34441</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="E7" s="2" t="n">
-        <v>42233</v>
+        <v>47980</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5498,35 +5545,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>60230</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5544,36 +5587,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="E9" s="2" t="n">
-        <v>60230</v>
+      <c r="D9" s="2" t="n">
+        <v>33995</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5583,50 +5626,8 @@
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>St Hyacinthe Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5636,7 +5637,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33492</v>
+        <v>33992</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -748,25 +748,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>33992</v>
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -781,41 +797,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>50530</v>
+        <v>34992</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35005</v>
+        <v>34895</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>36197</v>
+        <v>48940</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -864,18 +864,14 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -883,25 +879,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n">
-        <v>34992</v>
+        <v>33995</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>51023</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -916,7 +928,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -924,14 +936,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -941,16 +953,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -977,10 +989,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -990,16 +1002,16 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1022,33 +1034,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34985</v>
+        <v>34995</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>60543</v>
+        <v>42511</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -5165,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5253,36 +5257,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>34441</v>
+        <v>35005</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>36197</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5290,48 +5301,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>42233</v>
+        <v>33492</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5344,31 +5352,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>56845</v>
+        <v>34441</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -5380,7 +5381,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5388,16 +5389,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5405,23 +5402,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>34441</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>66091</v>
+        <v>42233</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -5433,7 +5430,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5446,35 +5443,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -5486,7 +5479,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5494,45 +5487,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5545,31 +5549,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5587,47 +5595,89 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="2" t="n">
-        <v>33995</v>
+      <c r="E9" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5637,6 +5687,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -600,41 +600,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32995</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>37000</v>
+        <v>32892</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -649,25 +633,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32892</v>
+        <v>34998</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -682,32 +666,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>35005</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>12755</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -733,7 +737,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -782,7 +786,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -815,7 +819,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34895</v>
+        <v>34699</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>48940</v>
+        <v>64022</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -855,16 +859,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -879,7 +883,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -887,14 +891,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33995</v>
+        <v>34985</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>51023</v>
+        <v>60543</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -904,16 +908,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -928,41 +932,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2023</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>64022</v>
-      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -971,128 +956,8 @@
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>60543</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>42511</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1105,9 +970,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5169,7 +5031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5257,7 +5119,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5265,35 +5127,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35005</v>
+        <v>33995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>36197</v>
+        <v>51023</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5301,45 +5163,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5352,36 +5217,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>34441</v>
+        <v>32995</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>37000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5394,7 +5266,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5402,35 +5274,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34441</v>
+        <v>34895</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>42233</v>
+        <v>48940</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5443,43 +5315,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>56845</v>
+        <v>33492</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5487,48 +5352,33 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -5536,7 +5386,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5549,40 +5399,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>42233</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5595,36 +5448,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2024</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>32911</v>
+      </c>
       <c r="E9" s="2" t="n">
-        <v>60230</v>
+        <v>56845</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5632,52 +5492,197 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
+        <v>34441</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>42233</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AutoTrader, Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="E11" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
         <v>33995</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5688,6 +5693,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -801,25 +801,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n">
-        <v>34992</v>
+        <v>34895</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -846,10 +862,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -859,16 +875,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -883,41 +899,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>60543</v>
-      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -926,38 +923,8 @@
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -969,7 +936,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5031,7 +4997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5119,43 +5085,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>51023</v>
+        <v>34992</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5168,7 +5127,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5176,35 +5135,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34995</v>
+        <v>34699</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>42511</v>
+        <v>64022</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5217,38 +5176,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32995</v>
+        <v>33995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37000</v>
+        <v>51023</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5266,7 +5225,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5274,14 +5233,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34895</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>48940</v>
+        <v>42511</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5290,14 +5249,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5315,36 +5274,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>33492</v>
+        <v>32995</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>37000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5365,7 +5331,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5374,19 +5340,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5399,38 +5365,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5448,22 +5407,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5472,19 +5431,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5492,44 +5451,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -5541,7 +5492,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5549,45 +5500,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E11" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5600,31 +5562,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5642,47 +5608,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" s="2" t="n">
-        <v>33995</v>
+      <c r="E13" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5696,6 +5704,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30992</v>
+        <v>29992</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -581,18 +581,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -607,7 +603,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32892</v>
+        <v>30992</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -618,14 +614,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -633,25 +633,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34998</v>
+        <v>32892</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -666,52 +666,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35005</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>12755</v>
+        <v>34998</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -737,7 +717,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -782,11 +762,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -813,10 +793,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34895</v>
+        <v>35005</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>48940</v>
+        <v>36197</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -835,14 +815,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -862,10 +846,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34985</v>
+        <v>34895</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>60543</v>
+        <v>48940</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -875,16 +859,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sunroof, CarPlay, Android Auto, Navigation, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -914,7 +898,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -4997,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5085,24 +5069,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -5114,7 +5105,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5127,34 +5118,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5176,7 +5160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5184,35 +5168,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5225,7 +5209,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5233,30 +5217,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5274,22 +5258,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32995</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37000</v>
+        <v>42511</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5298,14 +5282,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5323,36 +5307,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>33492</v>
+        <v>32995</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37000</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5373,7 +5364,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5382,19 +5373,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5407,38 +5398,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5456,22 +5440,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5480,19 +5464,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5500,44 +5484,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -5549,7 +5525,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5557,45 +5533,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E12" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5608,31 +5595,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="E13" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5650,47 +5641,89 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" s="2" t="n">
-        <v>33995</v>
+      <c r="E14" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5705,6 +5738,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -596,25 +596,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30992</v>
+        <v>30998</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>59938</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -623,7 +639,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31,992 → 30,992</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -640,7 +656,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32892</v>
+        <v>30792</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -651,14 +667,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -666,32 +686,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>32492</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -699,25 +723,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33992</v>
+        <v>34998</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -732,48 +756,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>33892</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -793,10 +805,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>35005</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>36197</v>
+        <v>50530</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -811,22 +823,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -868,7 +876,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -898,7 +906,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -5081,19 +5089,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34985</v>
+        <v>35005</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60543</v>
+        <v>36197</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -5105,7 +5113,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5113,29 +5121,40 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -5147,7 +5166,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5160,34 +5179,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5209,7 +5221,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5217,35 +5229,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5258,7 +5270,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5266,30 +5278,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5307,22 +5319,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32995</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37000</v>
+        <v>42511</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5331,14 +5343,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5376,7 +5388,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5418,7 +5430,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5467,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5516,7 +5528,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5573,7 +5585,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5619,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5661,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5703,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>35005</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>50530</v>
+        <v>26046</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -854,10 +858,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34895</v>
+        <v>33995</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>48940</v>
+        <v>50530</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -872,11 +876,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -891,32 +895,85 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>48940</v>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Lefebvre Toyota</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -928,6 +985,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4989,7 +5047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5089,22 +5147,22 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35005</v>
+        <v>34985</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>36197</v>
+        <v>60543</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5113,7 +5171,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5121,43 +5179,32 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>60543</v>
+        <v>34992</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5166,7 +5213,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5179,27 +5226,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>34992</v>
+        <v>34699</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>64022</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5221,7 +5275,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5229,35 +5283,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34699</v>
+        <v>33995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>64022</v>
+        <v>51023</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5270,7 +5324,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5278,30 +5332,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51023</v>
+        <v>42511</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5319,43 +5373,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>42511</v>
+        <v>33492</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5376,7 +5423,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>33492</v>
+        <v>34441</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5385,19 +5432,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5410,31 +5457,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
         <v>34441</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>42233</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5452,22 +5506,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>42233</v>
+        <v>56845</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5476,59 +5530,67 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5537,7 +5599,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5545,56 +5607,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>34441</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>42233</v>
+        <v>47980</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5607,35 +5658,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="E13" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>60230</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5653,36 +5700,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="E14" s="2" t="n">
-        <v>60230</v>
+      <c r="D14" s="2" t="n">
+        <v>33995</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5692,50 +5739,8 @@
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>St Hyacinthe Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5750,7 +5755,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,32 +563,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29992</v>
+        <v>30998</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>17345</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -596,52 +616,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30998</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>59938</v>
+        <v>29992</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>35005</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26046</v>
+        <v>50530</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -823,22 +823,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -858,10 +854,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -876,18 +872,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -895,85 +895,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>48940</v>
-      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -985,7 +932,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5047,7 +4993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5147,22 +5093,22 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34985</v>
+        <v>35005</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60543</v>
+        <v>26046</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5171,7 +5117,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5179,29 +5125,40 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -5213,7 +5170,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5226,34 +5183,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5275,7 +5225,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5283,35 +5233,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5324,7 +5274,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5332,30 +5282,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5373,36 +5323,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5423,7 +5380,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5432,19 +5389,19 @@
         </is>
       </c>
       <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5457,38 +5414,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5506,22 +5456,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5530,19 +5480,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5550,44 +5500,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -5599,7 +5541,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5607,45 +5549,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E12" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5658,31 +5611,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="E13" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5700,47 +5657,89 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" s="2" t="n">
-        <v>33995</v>
+      <c r="E14" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5755,6 +5754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,52 +563,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30998</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>17345</v>
+        <v>29992</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -623,7 +603,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29992</v>
+        <v>30792</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -634,14 +614,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -656,7 +640,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -667,7 +651,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -676,7 +660,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -686,36 +670,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32492</v>
+        <v>34998</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -723,32 +703,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34998</v>
+        <v>33892</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -756,36 +740,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>33892</v>
+        <v>33995</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -805,10 +801,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -823,18 +819,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -842,85 +842,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2023</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>48940</v>
-      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -931,7 +878,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4993,7 +4939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5081,11 +5027,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5093,10 +5039,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35005</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>26046</v>
+        <v>17345</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5105,19 +5051,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5127,7 +5073,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -5146,22 +5092,22 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34985</v>
+        <v>35005</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60543</v>
+        <v>26046</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5170,7 +5116,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5178,29 +5124,40 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -5212,7 +5169,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5225,34 +5182,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5274,7 +5224,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5282,35 +5232,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5323,7 +5273,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5331,30 +5281,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5372,36 +5322,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5422,7 +5379,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5431,19 +5388,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5456,38 +5413,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5505,22 +5455,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5529,19 +5479,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5549,44 +5499,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
@@ -5598,7 +5540,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5606,45 +5548,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E13" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5657,31 +5610,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5699,47 +5656,89 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>33995</v>
+      <c r="E15" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5755,6 +5754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,32 +563,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29992</v>
+        <v>30998</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5492</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -614,7 +634,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -640,7 +660,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32492</v>
+        <v>30992</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -651,18 +671,14 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -670,32 +686,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>32492</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -710,29 +730,25 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33892</v>
+        <v>32794</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -740,41 +756,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>50530</v>
+        <v>34998</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -789,41 +789,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>48940</v>
+        <v>33892</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -832,7 +816,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -842,22 +826,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2023</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>50530</v>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -866,8 +869,110 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34795</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>60062</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -878,6 +983,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4939,7 +5046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5027,43 +5134,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>30998</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>17345</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5071,52 +5168,41 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>35005</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>26046</v>
+        <v>29992</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5124,11 +5210,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5145,22 +5227,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34985</v>
+        <v>35005</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60543</v>
+        <v>26046</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5169,7 +5251,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5177,29 +5259,40 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -5211,7 +5304,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5224,34 +5317,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5273,7 +5359,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5281,35 +5367,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5322,7 +5408,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5330,30 +5416,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5371,36 +5457,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5421,7 +5514,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5430,19 +5523,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5455,38 +5548,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5504,22 +5590,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5528,19 +5614,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5548,44 +5634,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -5597,7 +5675,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5605,45 +5683,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5656,31 +5745,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="E15" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5698,47 +5791,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>33995</v>
+      <c r="E16" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5755,6 +5890,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5492</v>
+        <v>59938</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34888</v>
+        <v>33865</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>48940</v>
+        <v>65205</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -967,12 +967,114 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>35,025 → 35,005 → 33,865</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -985,6 +1087,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5046,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5151,7 +5255,7 @@
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5193,7 +5297,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5227,22 +5331,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35005</v>
+        <v>34985</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26046</v>
+        <v>60543</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5251,7 +5355,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5259,43 +5363,32 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>60543</v>
+        <v>34992</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5304,7 +5397,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5317,27 +5410,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>34992</v>
+        <v>34699</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>64022</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5359,7 +5459,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5367,35 +5467,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34699</v>
+        <v>33995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>64022</v>
+        <v>51023</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5408,7 +5508,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5416,30 +5516,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>51023</v>
+        <v>42511</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5457,43 +5557,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>42511</v>
+        <v>33492</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5514,7 +5607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>33492</v>
+        <v>34441</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5523,19 +5616,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5548,31 +5641,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
         <v>34441</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>42233</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5590,22 +5690,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42233</v>
+        <v>56845</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5614,59 +5714,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5675,7 +5783,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5683,56 +5791,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>34441</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>42233</v>
+        <v>47980</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5745,35 +5842,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="E15" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>60230</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5791,36 +5884,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="E16" s="2" t="n">
-        <v>60230</v>
+      <c r="D16" s="2" t="n">
+        <v>33995</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5830,50 +5923,8 @@
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>St Hyacinthe Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5890,7 +5941,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30998</v>
+        <v>24998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59938</v>
+        <v>48500</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,18 +597,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -616,25 +612,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30792</v>
+        <v>30998</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>17345</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -643,7 +655,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -653,32 +665,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>30992</v>
+        <v>33865</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>35000</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -686,36 +718,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>32492</v>
+        <v>33995</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -723,21 +767,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>32794</v>
+        <v>34990</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>48677</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -764,6 +824,9 @@
       </c>
       <c r="E8" s="2" t="n">
         <v>34998</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>66961</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -774,7 +837,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -783,298 +846,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>33892</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>19</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>33865</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>65205</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>48940</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>9</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1083,12 +856,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5150,7 +4917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5245,17 +5012,20 @@
         <v>2023</v>
       </c>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
+        <v>33892</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5264,7 +5034,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5272,7 +5042,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5285,7 +5059,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>29992</v>
+        <v>32492</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5294,19 +5068,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5314,48 +5088,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>60543</v>
+        <v>30792</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5363,41 +5134,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>34992</v>
+        <v>34888</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5405,48 +5187,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34699</v>
+        <v>34795</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>64022</v>
+        <v>60062</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5459,43 +5245,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>51023</v>
+        <v>30992</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5508,43 +5287,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>42511</v>
+        <v>32794</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5564,29 +5336,26 @@
         <v>2023</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="2" t="n">
-        <v>33492</v>
-      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5607,7 +5376,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34441</v>
+        <v>29992</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5616,19 +5385,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5641,7 +5410,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5649,35 +5418,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34441</v>
+        <v>34985</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42233</v>
+        <v>60543</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5690,43 +5459,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>56845</v>
+        <v>34992</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5734,16 +5496,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5751,39 +5509,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34441</v>
+        <v>34699</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>64022</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5796,40 +5550,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>33995</v>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>51023</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5842,15 +5599,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>34995</v>
+      </c>
       <c r="E15" s="2" t="n">
-        <v>60230</v>
+        <v>42511</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5859,19 +5623,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5892,39 +5656,366 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>33995</v>
+        <v>33492</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>34441</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>34441</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>42233</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>13</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>32911</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>56845</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34441</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>42233</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AutoTrader, Otogo.ca</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="E21" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
         <v>16</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="E22" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5941,6 +6032,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24998</v>
+        <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>48500</v>
+        <v>17345</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,14 +597,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -612,22 +616,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30998</v>
+        <v>31998</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17345</v>
+        <v>25996</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -646,18 +650,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -680,7 +680,7 @@
         <v>33865</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35000</v>
+        <v>50144</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -767,22 +767,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34990</v>
+        <v>34795</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48677</v>
+        <v>60062</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -792,16 +792,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -816,38 +816,136 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" t="n">
         <v>2024</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>34998</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>66961</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -856,6 +954,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5005,36 +5105,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>33892</v>
+        <v>24998</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5042,11 +5149,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5059,7 +5162,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5071,7 +5174,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5090,7 +5193,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5208,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5117,7 +5220,7 @@
         <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5136,45 +5239,38 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5189,29 +5285,29 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5220,14 +5316,14 @@
         </is>
       </c>
       <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5240,7 +5336,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5265,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5307,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5346,7 +5446,7 @@
         <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5388,7 +5488,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5437,7 +5537,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5479,7 +5579,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5528,7 +5628,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5577,7 +5677,7 @@
         <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5626,7 +5726,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5668,7 +5768,7 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5710,7 +5810,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5759,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5808,7 +5908,7 @@
         <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5865,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5911,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5953,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5995,7 +6095,7 @@
         <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>17345</v>
+        <v>22308</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -624,14 +624,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31998</v>
+        <v>33995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25996</v>
+        <v>50530</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -646,11 +646,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -665,22 +665,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33865</v>
+        <v>34795</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>50144</v>
+        <v>60062</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -699,18 +699,14 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -730,10 +726,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -748,11 +744,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -767,22 +763,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34795</v>
+        <v>34990</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60062</v>
+        <v>48677</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -792,12 +788,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -816,41 +812,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34888</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>48940</v>
+        <v>66961</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -859,93 +842,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>66961</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -954,8 +852,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5017,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5117,10 +5013,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>24998</v>
+        <v>33865</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>48500</v>
+        <v>50144</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5129,19 +5025,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5149,41 +5045,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>33892</v>
+        <v>31998</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>25996</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5191,45 +5098,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>32492</v>
+        <v>24998</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5237,11 +5147,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5254,7 +5160,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>30792</v>
+        <v>33892</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5266,7 +5172,7 @@
         <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5285,45 +5191,38 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>48940</v>
+        <v>32492</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5338,7 +5237,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5252,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>30992</v>
+        <v>30792</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5362,14 +5261,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5382,36 +5281,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>32794</v>
+        <v>34888</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5424,7 +5334,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5436,26 +5350,29 @@
         <v>2023</v>
       </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>30992</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5476,28 +5393,28 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>29992</v>
+        <v>32794</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5510,43 +5427,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>60543</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5567,7 +5474,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34992</v>
+        <v>29992</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5579,16 +5486,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5613,19 +5520,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>9</v>
@@ -5637,7 +5544,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5650,43 +5557,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>51023</v>
+        <v>34992</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5699,7 +5599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5707,35 +5607,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34995</v>
+        <v>34699</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42511</v>
+        <v>64022</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5748,36 +5648,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>33492</v>
+        <v>33995</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>51023</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
         <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5790,36 +5697,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>34441</v>
+        <v>34995</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5832,43 +5746,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>42233</v>
+        <v>33492</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5881,31 +5788,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>56845</v>
+        <v>34441</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
@@ -5917,7 +5817,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5925,11 +5825,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5951,30 +5847,26 @@
       <c r="E20" s="2" t="n">
         <v>42233</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5987,40 +5879,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>32911</v>
+      </c>
       <c r="E21" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -6028,41 +5923,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E22" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>17</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6082,13 +5992,17 @@
         <v>2023</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -6099,23 +6013,107 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>19</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6139,6 +6137,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>22308</v>
+        <v>59938</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -624,14 +624,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33995</v>
+        <v>31998</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>50530</v>
+        <v>54169</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -646,11 +646,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -665,22 +665,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34795</v>
+        <v>33995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60062</v>
+        <v>50530</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -695,11 +695,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -714,22 +714,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34888</v>
+        <v>34795</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>48940</v>
+        <v>60062</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34990</v>
+        <v>34888</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48677</v>
+        <v>48940</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -788,16 +788,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -812,38 +812,87 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>2024</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>34998</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>66961</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>22</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -852,6 +901,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4913,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5028,7 +5078,7 @@
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5054,7 +5104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5062,14 +5112,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>31998</v>
+        <v>24998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>25996</v>
+        <v>48500</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5081,16 +5131,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5103,43 +5153,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>24998</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>48500</v>
+        <v>33892</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5147,7 +5190,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5160,7 +5207,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>33892</v>
+        <v>32492</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5172,7 +5219,7 @@
         <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5191,7 +5238,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5253,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>32492</v>
+        <v>30792</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5218,7 +5265,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5237,38 +5284,45 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>30792</v>
+        <v>34888</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5283,45 +5337,38 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>48940</v>
+        <v>30992</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5334,11 +5381,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5351,19 +5394,19 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>30992</v>
+        <v>32794</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5392,29 +5435,26 @@
         <v>2023</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>32794</v>
-      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5434,21 +5474,24 @@
         <v>2023</v>
       </c>
       <c r="C11" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>29992</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5466,36 +5509,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>29992</v>
+        <v>34985</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5508,34 +5558,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>60543</v>
+        <v>34992</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5544,7 +5587,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5557,27 +5600,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>34992</v>
+        <v>34699</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>64022</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5599,7 +5649,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5607,35 +5657,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34699</v>
+        <v>33995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>64022</v>
+        <v>51023</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5648,7 +5698,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5656,30 +5706,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>51023</v>
+        <v>42511</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5697,43 +5747,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>42511</v>
+        <v>33492</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5754,7 +5797,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>33492</v>
+        <v>34441</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5763,19 +5806,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5788,31 +5831,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
         <v>34441</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>42233</v>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5830,22 +5880,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42233</v>
+        <v>56845</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -5854,59 +5904,67 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5915,7 +5973,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5923,56 +5981,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>34441</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="E22" s="2" t="n">
-        <v>42233</v>
+        <v>47980</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5985,35 +6032,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="E23" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>60230</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6031,36 +6074,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="E24" s="2" t="n">
-        <v>60230</v>
+      <c r="D24" s="2" t="n">
+        <v>33995</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>St Hyacinthe Mitsubishi</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6070,50 +6113,8 @@
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>St Hyacinthe Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>19</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6138,7 +6139,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59938</v>
+        <v>44376</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -616,22 +616,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31998</v>
+        <v>34795</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54169</v>
+        <v>60062</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -695,11 +695,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -714,22 +714,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34795</v>
+        <v>34990</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60062</v>
+        <v>48677</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -763,41 +763,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>34888</v>
+        <v>32999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48940</v>
+        <v>55369</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -812,41 +799,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>48677</v>
+        <v>66961</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -855,44 +829,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>66961</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -901,7 +839,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4963,7 +4900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5063,31 +5000,31 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33865</v>
+        <v>33995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50144</v>
+        <v>50530</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5095,16 +5032,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5112,14 +5045,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>24998</v>
+        <v>31998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48500</v>
+        <v>54169</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5128,19 +5061,19 @@
         </is>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5153,36 +5086,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>33892</v>
+        <v>33865</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50144</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5192,43 +5132,50 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>35,025 → 35,005 → 33,865</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>32492</v>
+        <v>24998</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5236,11 +5183,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5253,7 +5196,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>30792</v>
+        <v>33892</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5265,7 +5208,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5284,45 +5227,38 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>48940</v>
+        <v>32492</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5337,7 +5273,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5288,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>30992</v>
+        <v>30792</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5361,14 +5297,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5381,36 +5317,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>32794</v>
+        <v>34888</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5423,7 +5370,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5435,26 +5386,29 @@
         <v>2023</v>
       </c>
       <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>30992</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5475,28 +5429,28 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>29992</v>
+        <v>32794</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5509,43 +5463,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>60543</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5566,7 +5510,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34992</v>
+        <v>29992</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5578,16 +5522,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5612,19 +5556,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>11</v>
@@ -5636,7 +5580,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5649,43 +5593,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>51023</v>
+        <v>34992</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5698,7 +5635,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5706,35 +5643,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34995</v>
+        <v>34699</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>42511</v>
+        <v>64022</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5747,36 +5684,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>33492</v>
+        <v>33995</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>51023</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5789,36 +5733,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>34441</v>
+        <v>34995</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5831,43 +5782,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>42233</v>
+        <v>33492</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5880,31 +5824,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>56845</v>
+        <v>34441</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
         <v>17</v>
@@ -5916,7 +5853,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5924,11 +5861,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5950,30 +5883,26 @@
       <c r="E21" s="2" t="n">
         <v>42233</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5986,40 +5915,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>32911</v>
+      </c>
       <c r="E22" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6027,41 +5959,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E23" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6081,13 +6028,17 @@
         <v>2023</v>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>47980</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -6098,23 +6049,107 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="E25" s="2" t="n">
+        <v>60230</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>St Hyacinthe Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6139,6 +6174,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44376</v>
+        <v>59938</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -690,16 +690,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34990</v>
+        <v>33865</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>48677</v>
+        <v>68766</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -739,23 +739,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -784,7 +788,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -820,7 +824,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -4988,43 +4992,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33995</v>
+        <v>34795</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50530</v>
+        <v>60062</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5037,7 +5041,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5045,14 +5049,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>31998</v>
+        <v>34888</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54169</v>
+        <v>48940</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5061,7 +5065,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -5073,7 +5077,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5098,31 +5102,31 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33865</v>
+        <v>33995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50144</v>
+        <v>50530</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5130,16 +5134,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5147,14 +5147,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>24998</v>
+        <v>31998</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>48500</v>
+        <v>54169</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5163,19 +5163,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5188,36 +5188,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>33892</v>
+        <v>24998</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5225,11 +5232,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5242,7 +5245,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5254,7 +5257,7 @@
         <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5273,7 +5276,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5291,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5300,7 +5303,7 @@
         <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5319,45 +5322,38 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5372,38 +5368,45 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>30992</v>
+        <v>34888</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5416,7 +5419,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5429,19 +5436,19 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>32794</v>
+        <v>30992</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5470,26 +5477,29 @@
         <v>2023</v>
       </c>
       <c r="C12" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
+        <v>32794</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5509,24 +5519,21 @@
         <v>2023</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" s="2" t="n">
-        <v>29992</v>
-      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5544,43 +5551,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>60543</v>
+        <v>29992</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5593,24 +5593,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>12</v>
@@ -5622,7 +5629,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5635,34 +5642,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5692,35 +5692,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5733,7 +5733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5782,36 +5782,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5832,7 +5839,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -5841,19 +5848,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5866,38 +5873,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5915,22 +5915,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -5939,19 +5939,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5959,44 +5959,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
@@ -6008,7 +6000,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6016,45 +6008,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E24" s="2" t="n">
-        <v>47980</v>
+        <v>42233</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6067,31 +6070,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="E25" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>47980</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -6109,36 +6116,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>33995</v>
+      <c r="E26" s="2" t="n">
+        <v>60230</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>St Hyacinthe Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>21</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$26</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,32 +530,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5000</v>
+        <v>33003</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>41000</v>
+        <v>52696</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -563,22 +583,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59938</v>
+        <v>67680</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -588,27 +608,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -616,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -650,7 +666,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -699,7 +715,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -714,52 +730,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="n">
-        <v>33865</v>
+        <v>32999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>68766</v>
+        <v>55369</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -767,28 +766,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>55369</v>
+        <v>67016</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -797,44 +796,8 @@
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>66961</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -842,7 +805,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4992,43 +4954,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>34795</v>
+        <v>5000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60062</v>
+        <v>41000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5041,11 +4996,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5053,10 +5008,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34888</v>
+        <v>30998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48940</v>
+        <v>59938</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5065,19 +5020,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5085,48 +5040,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33995</v>
+        <v>34795</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50530</v>
+        <v>60062</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5139,22 +5098,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>31998</v>
+        <v>34795</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54169</v>
+        <v>60062</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5163,19 +5122,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5200,31 +5159,31 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>24998</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48500</v>
+        <v>50530</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5237,36 +5196,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>33892</v>
+        <v>31998</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5274,45 +5240,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>32492</v>
+        <v>24998</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5320,11 +5289,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5337,7 +5302,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>30792</v>
+        <v>33892</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5349,7 +5314,7 @@
         <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5368,45 +5333,38 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>48940</v>
+        <v>32492</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5421,7 +5379,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5394,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>30992</v>
+        <v>30792</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5445,14 +5403,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5465,36 +5423,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>32794</v>
+        <v>34888</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5507,7 +5476,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5519,26 +5492,29 @@
         <v>2023</v>
       </c>
       <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
+        <v>30992</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5559,28 +5535,28 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>29992</v>
+        <v>32794</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5593,43 +5569,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>60543</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5650,7 +5616,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34992</v>
+        <v>29992</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5662,16 +5628,16 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5696,19 +5662,19 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34699</v>
+        <v>34985</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>64022</v>
+        <v>60543</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
@@ -5720,7 +5686,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5733,43 +5699,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>51023</v>
+        <v>34992</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5782,7 +5741,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5790,35 +5749,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34995</v>
+        <v>34699</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42511</v>
+        <v>64022</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5831,36 +5790,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>33492</v>
+        <v>33995</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>51023</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
         <v>15</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5873,36 +5839,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
-        <v>34441</v>
+        <v>34995</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5915,43 +5888,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>42233</v>
+        <v>33492</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5964,31 +5930,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>56845</v>
+        <v>34441</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
@@ -6000,7 +5959,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6008,11 +5967,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6034,30 +5989,26 @@
       <c r="E24" s="2" t="n">
         <v>42233</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader, Otogo.ca</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6070,40 +6021,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>32911</v>
+      </c>
       <c r="E25" s="2" t="n">
-        <v>47980</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+        <v>56845</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -6111,41 +6065,56 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>35,473 → 32,911</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>34441</v>
+      </c>
       <c r="E26" s="2" t="n">
-        <v>60230</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>42233</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Otogo.ca</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>21</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33003</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>52696</v>
+        <v>59938</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>34997</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67680</v>
+        <v>14634</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -632,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34888</v>
+        <v>34795</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>48940</v>
+        <v>60062</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -689,14 +689,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>48677</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -711,11 +711,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,28 +730,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>32999</v>
+        <v>34888</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55369</v>
+        <v>48940</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -766,38 +779,123 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>55369</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>2024</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>34998</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>67016</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>26</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>27</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -805,6 +903,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4866,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4954,36 +5054,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>5000</v>
+        <v>33003</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>41000</v>
+        <v>52696</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4991,43 +5098,40 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>30998</v>
+        <v>5000</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>59938</v>
+        <v>41000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5040,11 +5144,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5073,19 +5173,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5098,43 +5198,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34795</v>
+        <v>33995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60062</v>
+        <v>50530</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5147,7 +5247,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5155,30 +5255,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>31998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>50530</v>
+        <v>54169</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5196,7 +5296,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5204,14 +5304,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>31998</v>
+        <v>24998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54169</v>
+        <v>48500</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5220,19 +5320,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5245,43 +5345,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>24998</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>48500</v>
+        <v>33892</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5289,7 +5382,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5302,7 +5399,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>33892</v>
+        <v>32492</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5314,7 +5411,7 @@
         <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5333,7 +5430,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5445,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>32492</v>
+        <v>30792</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5360,7 +5457,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5379,38 +5476,45 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>30792</v>
+        <v>34888</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5425,45 +5529,38 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>48940</v>
+        <v>30992</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5476,11 +5573,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5493,19 +5586,19 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>30992</v>
+        <v>32794</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5534,29 +5627,26 @@
         <v>2023</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" s="2" t="n">
-        <v>32794</v>
-      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5576,21 +5666,24 @@
         <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>29992</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5608,36 +5701,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>29992</v>
+        <v>34985</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5650,34 +5750,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>60543</v>
+        <v>34992</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5686,7 +5779,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5699,27 +5792,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>34992</v>
+        <v>34699</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>64022</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5741,7 +5841,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5749,35 +5849,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34699</v>
+        <v>33995</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>64022</v>
+        <v>51023</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5790,7 +5890,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5798,30 +5898,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33995</v>
+        <v>34995</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>51023</v>
+        <v>42511</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5839,43 +5939,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>42511</v>
+        <v>33492</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5896,7 +5989,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>33492</v>
+        <v>34441</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -5905,19 +5998,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5930,31 +6023,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2023</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="n">
         <v>34441</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>42233</v>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5972,22 +6072,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>34441</v>
+        <v>32911</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>42233</v>
+        <v>56845</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -5996,136 +6096,34 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>32911</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>56845</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>35,473 → 32,911</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AutoTrader, Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>21</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M26"/>
+  <autoFilter ref="A1:M24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6150,8 +6148,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -583,22 +583,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34997</v>
+        <v>34795</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14634</v>
+        <v>60062</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34795</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -689,14 +689,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34888</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>48940</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -755,16 +755,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,41 +779,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>34990</v>
+        <v>32999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48677</v>
+        <v>55369</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -828,28 +815,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>55369</v>
+        <v>67016</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -858,44 +845,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>67016</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>27</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -904,7 +855,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5054,7 +5004,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5062,14 +5012,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33003</v>
+        <v>34997</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>52696</v>
+        <v>14634</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5078,19 +5028,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5098,45 +5048,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>5000</v>
+        <v>33003</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>41000</v>
+        <v>52696</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5144,48 +5097,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34795</v>
+        <v>5000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60062</v>
+        <v>41000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5198,43 +5148,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33995</v>
+        <v>34795</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>50530</v>
+        <v>60062</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5247,7 +5197,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5255,30 +5205,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>31998</v>
+        <v>33995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54169</v>
+        <v>50530</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5296,7 +5246,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5304,14 +5254,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24998</v>
+        <v>31998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48500</v>
+        <v>54169</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5320,19 +5270,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5345,36 +5295,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>33892</v>
+        <v>24998</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5382,11 +5339,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5399,7 +5352,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5411,7 +5364,7 @@
         <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5430,7 +5383,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5398,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5457,7 +5410,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5476,45 +5429,38 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5529,38 +5475,45 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>30992</v>
+        <v>34888</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5573,7 +5526,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5586,19 +5543,19 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>32794</v>
+        <v>30992</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5627,26 +5584,29 @@
         <v>2023</v>
       </c>
       <c r="C14" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>32794</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5666,24 +5626,21 @@
         <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>29992</v>
-      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5701,43 +5658,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>60543</v>
+        <v>29992</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5750,24 +5700,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>15</v>
@@ -5779,7 +5736,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5792,34 +5749,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5841,7 +5791,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5849,35 +5799,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5890,7 +5840,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5898,30 +5848,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5939,36 +5889,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5989,7 +5946,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -5998,19 +5955,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6023,38 +5980,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2023</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
         <v>34441</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>42233</v>
-      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6072,22 +6022,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>32911</v>
+        <v>34441</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>56845</v>
+        <v>42233</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -6096,19 +6046,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6116,11 +6066,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>35,473 → 32,911</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M24"/>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,7 +545,7 @@
         <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>59938</v>
+        <v>64485</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -657,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5004,7 +5004,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5012,35 +5012,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34997</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14634</v>
+        <v>67680</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5053,7 +5053,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5061,14 +5061,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>33003</v>
+        <v>34997</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>52696</v>
+        <v>14634</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5077,19 +5077,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5097,45 +5097,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>5000</v>
+        <v>33003</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>41000</v>
+        <v>52696</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5143,48 +5146,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>34795</v>
+        <v>5000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60062</v>
+        <v>41000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5197,43 +5197,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33995</v>
+        <v>34795</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>50530</v>
+        <v>60062</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5254,30 +5254,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>31998</v>
+        <v>33995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54169</v>
+        <v>50530</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5303,14 +5303,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24998</v>
+        <v>31998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48500</v>
+        <v>54169</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5319,19 +5319,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5344,36 +5344,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>33892</v>
+        <v>24998</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5381,11 +5388,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5398,7 +5401,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5410,7 +5413,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5429,7 +5432,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5447,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5456,7 +5459,7 @@
         <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5475,45 +5478,38 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I12" t="n">
         <v>9</v>
       </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5528,38 +5524,45 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>30992</v>
+        <v>34888</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5572,7 +5575,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5585,19 +5592,19 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>32794</v>
+        <v>30992</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5626,26 +5633,29 @@
         <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>32794</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5665,24 +5675,21 @@
         <v>2023</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>29992</v>
-      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5700,43 +5707,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>60543</v>
+        <v>29992</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5749,24 +5749,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>16</v>
@@ -5778,7 +5785,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5791,34 +5798,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5848,35 +5848,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5889,7 +5889,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5897,30 +5897,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5938,36 +5938,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5988,7 +5995,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>34441</v>
+        <v>33492</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -5997,19 +6004,19 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6019,57 +6026,8 @@
       </c>
       <c r="M23" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>34441</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>42233</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>21</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6093,7 +6051,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>33003</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>64485</v>
+        <v>26596</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -657,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,41 +730,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="n">
-        <v>34990</v>
+        <v>32999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>48677</v>
+        <v>55369</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,28 +766,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>55369</v>
+        <v>67016</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -809,44 +796,8 @@
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>67016</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -854,7 +805,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4916,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5004,43 +4954,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67680</v>
+        <v>64485</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5048,12 +4998,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5061,14 +5015,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34997</v>
+        <v>34888</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14634</v>
+        <v>48940</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5077,19 +5031,19 @@
         </is>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5102,7 +5056,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5110,35 +5064,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33003</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52696</v>
+        <v>67680</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5146,45 +5100,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>5000</v>
+        <v>34997</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41000</v>
+        <v>14634</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5197,43 +5154,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34795</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60062</v>
+        <v>41000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5246,43 +5196,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>33995</v>
+        <v>34795</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50530</v>
+        <v>60062</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5295,7 +5245,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5303,30 +5253,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>31998</v>
+        <v>33995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54169</v>
+        <v>50530</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5344,7 +5294,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5352,14 +5302,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>24998</v>
+        <v>31998</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>48500</v>
+        <v>54169</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5368,19 +5318,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5393,36 +5343,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>33892</v>
+        <v>24998</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>48500</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5430,11 +5387,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5447,7 +5400,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5459,7 +5412,7 @@
         <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5478,7 +5431,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5446,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5505,7 +5458,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5524,45 +5477,38 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5577,38 +5523,45 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>30992</v>
+        <v>34888</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5621,7 +5574,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5634,19 +5591,19 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>32794</v>
+        <v>30992</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5675,26 +5632,29 @@
         <v>2023</v>
       </c>
       <c r="C16" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>32794</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5714,24 +5674,21 @@
         <v>2023</v>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="n">
-        <v>29992</v>
-      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5749,43 +5706,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>60543</v>
+        <v>29992</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5798,24 +5748,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>17</v>
@@ -5827,7 +5784,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5840,34 +5797,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5889,7 +5839,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5897,35 +5847,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -5938,7 +5888,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5946,30 +5896,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5987,47 +5937,96 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2023</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>33492</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6051,6 +6050,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33003</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26596</v>
+        <v>64485</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,22 +583,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34795</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>60062</v>
+        <v>19232</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>33003</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>41886</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,23 +657,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -681,7 +685,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -689,14 +693,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>48677</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,28 +734,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>32999</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55369</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -766,38 +783,123 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>55369</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>2024</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>34998</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>67016</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>30</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -805,6 +907,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4954,7 +5058,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4962,14 +5066,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>34795</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>64485</v>
+        <v>60062</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -4978,19 +5082,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4998,16 +5102,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5015,35 +5115,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34888</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48940</v>
+        <v>67680</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5056,7 +5156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5064,30 +5164,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>34888</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67680</v>
+        <v>48940</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5132,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5174,7 +5274,7 @@
         <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5223,7 +5323,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5272,7 +5372,7 @@
         <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5321,7 +5421,7 @@
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5370,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5412,7 +5512,7 @@
         <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5458,7 +5558,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5504,7 +5604,7 @@
         <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5557,7 +5657,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5603,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5645,7 +5745,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5684,7 +5784,7 @@
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5726,7 +5826,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5775,7 +5875,7 @@
         <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5817,7 +5917,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5866,7 +5966,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5915,7 +6015,7 @@
         <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5964,7 +6064,7 @@
         <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6006,7 +6106,7 @@
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>24998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>64485</v>
+        <v>23847</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,18 +564,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -617,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,7 +628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +636,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33003</v>
+        <v>35099</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>41886</v>
+        <v>33296</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,18 +662,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,7 +677,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -693,14 +685,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>33003</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>65205</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -715,18 +707,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -759,16 +755,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,7 +779,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -791,14 +787,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34990</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48677</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -817,7 +813,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,28 +828,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>32999</v>
+        <v>35099</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>55369</v>
+        <v>68226</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -868,38 +877,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67016</v>
+        <v>55369</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>67016</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>31</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -909,6 +954,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5058,7 +5104,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5066,14 +5112,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34795</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60062</v>
+        <v>64485</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5082,19 +5128,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5102,12 +5148,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5115,35 +5165,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67680</v>
+        <v>48677</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5156,22 +5206,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34888</v>
+        <v>34795</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>48940</v>
+        <v>60062</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5180,19 +5230,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5205,7 +5255,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5213,35 +5263,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34997</v>
+        <v>32495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14634</v>
+        <v>67680</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5254,36 +5304,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>5000</v>
+        <v>34888</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41000</v>
+        <v>48940</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5296,22 +5353,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34795</v>
+        <v>34997</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60062</v>
+        <v>14634</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5320,19 +5377,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5345,34 +5402,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>33995</v>
+        <v>5000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>50530</v>
+        <v>41000</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5381,7 +5431,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5394,22 +5444,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>31998</v>
+        <v>34795</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>54169</v>
+        <v>60062</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5418,19 +5468,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5455,31 +5505,31 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24998</v>
+        <v>33995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>48500</v>
+        <v>50530</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5492,36 +5542,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>33892</v>
+        <v>31998</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5529,11 +5586,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5546,7 +5599,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>32492</v>
+        <v>33892</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5558,7 +5611,7 @@
         <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5577,7 +5630,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5645,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>30792</v>
+        <v>32492</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5604,7 +5657,7 @@
         <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5623,45 +5676,38 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>48940</v>
+        <v>30792</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5676,38 +5722,45 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>30992</v>
+        <v>34888</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5720,7 +5773,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5733,19 +5790,19 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>32794</v>
+        <v>30992</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5774,26 +5831,29 @@
         <v>2023</v>
       </c>
       <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>32794</v>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5813,24 +5873,21 @@
         <v>2023</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>29992</v>
-      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5848,43 +5905,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>60543</v>
+        <v>29992</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5897,24 +5947,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>34992</v>
+        <v>34985</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>19</v>
@@ -5926,7 +5983,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5939,34 +5996,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>64022</v>
+        <v>34992</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5988,7 +6038,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5996,35 +6046,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>33995</v>
+        <v>34699</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>51023</v>
+        <v>64022</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6037,7 +6087,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6045,30 +6095,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>42511</v>
+        <v>51023</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6086,36 +6136,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="n">
-        <v>33492</v>
+        <v>34995</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>42511</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +587,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>33003</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19232</v>
+        <v>41886</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,14 +613,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -628,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -636,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>35099</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>33296</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -658,11 +662,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,7 +681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -685,14 +689,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33003</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65205</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -702,27 +706,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -730,11 +730,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>67531</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -760,11 +760,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,41 +779,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>32999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>55369</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -828,41 +815,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35099</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>68226</v>
+        <v>67016</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -884,21 +858,21 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32999</v>
+        <v>34990</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>55369</v>
+        <v>48677</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -907,44 +881,8 @@
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>67016</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>32</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -954,7 +892,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5016,7 +4953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5104,22 +5041,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>64485</v>
+        <v>19232</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5128,19 +5065,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5148,16 +5085,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5165,35 +5098,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34990</v>
+        <v>35099</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48677</v>
+        <v>33296</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5206,22 +5139,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34795</v>
+        <v>35099</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60062</v>
+        <v>68226</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5230,19 +5163,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5255,43 +5188,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32495</v>
+        <v>30998</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67680</v>
+        <v>64485</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5299,7 +5232,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5316,31 +5253,31 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5353,22 +5290,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34997</v>
+        <v>34795</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14634</v>
+        <v>60062</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5377,19 +5314,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5402,15 +5339,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>5000</v>
+        <v>32495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41000</v>
+        <v>67680</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5419,19 +5363,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5444,22 +5388,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5468,19 +5412,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5493,7 +5437,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5501,35 +5445,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>33995</v>
+        <v>34997</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>50530</v>
+        <v>14634</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5542,43 +5486,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>31998</v>
+        <v>5000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>54169</v>
+        <v>41000</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5591,36 +5528,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>33892</v>
+        <v>34795</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>60062</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5628,36 +5572,39 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>32492</v>
+        <v>33995</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5666,7 +5613,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5674,45 +5621,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>30792</v>
+        <v>31998</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5720,47 +5670,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>48940</v>
+        <v>33892</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5775,7 +5714,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5729,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>30992</v>
+        <v>32492</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5799,14 +5738,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5819,7 +5758,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5832,23 +5775,23 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>32794</v>
+        <v>30792</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5861,38 +5804,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>48940</v>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5900,7 +5857,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5913,7 +5874,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>29992</v>
+        <v>30992</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -5922,19 +5883,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5947,43 +5908,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>60543</v>
+        <v>32794</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -6003,29 +5957,26 @@
         <v>2023</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>34992</v>
-      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -6038,43 +5989,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>64022</v>
+        <v>29992</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6087,7 +6031,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6095,35 +6039,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>33995</v>
+        <v>34985</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>51023</v>
+        <v>60543</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Otogo.ca, AutoTrader, Kijiji</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6136,43 +6080,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>42511</v>
+        <v>34992</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6182,8 +6119,57 @@
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>34699</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>64022</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6208,6 +6194,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24998</v>
+        <v>35098</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>23847</v>
+        <v>33296</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,14 +564,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33003</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>41886</v>
+        <v>47938</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,18 +617,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>33003</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>68335</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -662,18 +662,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -693,10 +697,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,11 +734,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -742,10 +746,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34995</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67531</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -755,16 +759,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,28 +783,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>32999</v>
+        <v>35098</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>55369</v>
+        <v>68226</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -815,28 +832,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34998</v>
+        <v>34990</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67016</v>
+        <v>48677</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -851,38 +881,123 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>67531</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>2023</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="E10" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>55369</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>34</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -892,6 +1007,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4953,7 +5070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5041,7 +5158,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5049,14 +5166,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>24998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19232</v>
+        <v>23847</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5065,19 +5182,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5090,27 +5207,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>35099</v>
+        <v>34990</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33296</v>
+        <v>48677</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -5121,12 +5234,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5166,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5215,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5241,43 +5354,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34990</v>
+        <v>34795</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48677</v>
+        <v>60062</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5290,38 +5403,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34795</v>
+        <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5339,7 +5452,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5347,35 +5460,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32495</v>
+        <v>34888</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>67680</v>
+        <v>48940</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5388,7 +5501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5396,14 +5509,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34888</v>
+        <v>34997</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>48940</v>
+        <v>14634</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5412,19 +5525,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5437,43 +5550,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34997</v>
+        <v>5000</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14634</v>
+        <v>41000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5486,36 +5592,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>5000</v>
+        <v>34795</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>41000</v>
+        <v>60062</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5528,43 +5641,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34795</v>
+        <v>33995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60062</v>
+        <v>50530</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5577,7 +5690,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5585,30 +5698,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>33995</v>
+        <v>31998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>50530</v>
+        <v>54169</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5626,43 +5739,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>54169</v>
+        <v>33892</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5670,7 +5776,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5683,7 +5793,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>33892</v>
+        <v>32492</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5695,7 +5805,7 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5714,7 +5824,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5839,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>32492</v>
+        <v>30792</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5741,7 +5851,7 @@
         <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5760,38 +5870,45 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>30792</v>
+        <v>34888</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5806,45 +5923,38 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>48940</v>
+        <v>30992</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5857,11 +5967,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5874,19 +5980,19 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>30992</v>
+        <v>32794</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5915,29 +6021,26 @@
         <v>2023</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>32794</v>
-      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5957,21 +6060,24 @@
         <v>2023</v>
       </c>
       <c r="C21" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>29992</v>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5989,36 +6095,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="n">
-        <v>29992</v>
+        <v>34985</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>60543</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Giroux Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6028,148 +6141,8 @@
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>60543</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>20</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>21</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>34699</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>64022</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6192,9 +6165,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,22 +530,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>35098</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>33296</v>
+        <v>37000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,099 → 35,098</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,41 +583,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2023</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>27500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>47938</v>
+        <v>33173</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,7 +619,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +627,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33003</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>68335</v>
+        <v>47938</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,18 +653,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -719,7 +702,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +751,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -795,7 +778,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35098</v>
+        <v>34998</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>68226</v>
@@ -866,7 +849,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -881,41 +864,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67531</v>
+        <v>55369</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -930,28 +900,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55369</v>
+        <v>67017</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -960,44 +930,8 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>34</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1008,7 +942,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5070,7 +5003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5170,10 +5103,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>24998</v>
+        <v>33003</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>23847</v>
+        <v>68335</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5182,19 +5115,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5202,44 +5135,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48677</v>
+        <v>33296</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5247,27 +5188,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35099</v>
+        <v>34995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5276,19 +5221,19 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5301,22 +5246,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>30998</v>
+        <v>35098</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>64485</v>
+        <v>68226</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5325,19 +5270,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5345,31 +5290,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34795</v>
+        <v>24998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60062</v>
+        <v>23847</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5378,19 +5319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5403,43 +5344,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67680</v>
+        <v>48677</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5452,7 +5389,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5460,14 +5397,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34888</v>
+        <v>35099</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48940</v>
+        <v>68226</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5476,19 +5413,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5501,22 +5438,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34997</v>
+        <v>34795</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14634</v>
+        <v>60062</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5525,19 +5462,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5550,15 +5487,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>5000</v>
+        <v>32495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>41000</v>
+        <v>67680</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5567,19 +5511,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5592,22 +5536,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5616,19 +5560,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5641,7 +5585,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5649,35 +5593,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>33995</v>
+        <v>34997</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>50530</v>
+        <v>14634</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5690,43 +5634,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>31998</v>
+        <v>5000</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>54169</v>
+        <v>41000</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5739,36 +5676,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>33892</v>
+        <v>34795</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>60062</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5776,36 +5720,39 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>32492</v>
+        <v>33995</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5814,7 +5761,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5822,45 +5769,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>30792</v>
+        <v>31998</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5868,47 +5818,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>48940</v>
+        <v>33892</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5923,7 +5862,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5877,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>30992</v>
+        <v>32492</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5947,14 +5886,14 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5967,7 +5906,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5980,23 +5923,23 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>32794</v>
+        <v>30792</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -6009,38 +5952,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>48940</v>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -6048,7 +6005,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6061,7 +6022,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>29992</v>
+        <v>30992</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -6070,19 +6031,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -6095,43 +6056,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>34985</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>60543</v>
+        <v>32794</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Otogo.ca, Giroux Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -6141,8 +6095,89 @@
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>17</v>
+      </c>
+      <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>29992</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M22"/>
+  <autoFilter ref="A1:M24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6165,6 +6200,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,22 +530,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>37000</v>
+        <v>67680</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -560,22 +560,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,28 +579,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2023</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>27500</v>
+        <v>33495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>33173</v>
+        <v>52500</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -619,7 +628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -627,14 +636,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>47938</v>
+        <v>48677</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -644,16 +653,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -668,41 +677,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>32999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>55369</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -717,41 +713,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>34998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67017</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -760,188 +743,14 @@
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>68226</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>16</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>32999</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>55369</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>11</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>35</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5003,7 +4812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5091,11 +4900,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5103,10 +4912,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33003</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>68335</v>
+        <v>37000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5115,19 +4924,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5137,14 +4946,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5152,14 +4961,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>35098</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33296</v>
+        <v>47938</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5168,19 +4977,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5188,31 +4997,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>34995</v>
+        <v>27500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67531</v>
+        <v>33173</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5221,19 +5022,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5258,7 +5059,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>35098</v>
+        <v>34998</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>68226</v>
@@ -5277,12 +5078,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5307,10 +5108,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>24998</v>
+        <v>33003</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23847</v>
+        <v>68335</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5319,19 +5120,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5339,44 +5140,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48677</v>
+        <v>33296</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5384,27 +5193,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35099</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5413,19 +5226,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5438,22 +5251,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34795</v>
+        <v>35098</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60062</v>
+        <v>68226</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5462,19 +5275,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5487,7 +5300,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5495,35 +5308,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32495</v>
+        <v>24998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>67680</v>
+        <v>23847</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5536,43 +5349,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5585,7 +5394,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5593,14 +5402,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34997</v>
+        <v>35099</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14634</v>
+        <v>68226</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5612,16 +5421,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5634,36 +5443,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>5000</v>
+        <v>34795</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41000</v>
+        <v>60062</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5676,43 +5492,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34795</v>
+        <v>32495</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5737,31 +5553,31 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5774,7 +5590,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5782,14 +5598,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>31998</v>
+        <v>34997</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54169</v>
+        <v>14634</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5798,19 +5614,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5823,27 +5639,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>33892</v>
+        <v>5000</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>41000</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5852,7 +5668,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5860,45 +5676,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>32492</v>
+        <v>34795</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>60062</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5906,36 +5725,39 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>30792</v>
+        <v>33995</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5944,7 +5766,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5952,16 +5774,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5969,14 +5787,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34888</v>
+        <v>31998</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>48940</v>
+        <v>54169</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -5985,19 +5803,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -6005,11 +5823,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6022,7 +5836,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>30992</v>
+        <v>33892</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -6031,14 +5845,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6051,7 +5865,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6064,23 +5882,23 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>32794</v>
+        <v>32492</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6093,7 +5911,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6105,17 +5927,20 @@
         <v>2023</v>
       </c>
       <c r="C23" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>30792</v>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6124,7 +5949,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -6132,52 +5957,232 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="n">
-        <v>29992</v>
+        <v>34888</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>30992</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>32794</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
+        <v>29992</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="I24" t="n">
-        <v>17</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="I28" t="n">
+        <v>18</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6202,6 +6207,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32495</v>
+        <v>30500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67680</v>
+        <v>49170</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -560,18 +560,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33495</v>
+        <v>34998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52500</v>
+        <v>62599</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -604,12 +608,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -620,7 +624,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -628,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -636,14 +644,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>48677</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -653,16 +661,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -677,28 +685,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>32999</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55369</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -713,44 +734,181 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>34998</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>55369</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>13</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>67017</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>36</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>37</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4812,7 +4970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4927,7 +5085,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4980,7 +5138,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5025,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5047,22 +5205,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34998</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5071,19 +5229,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5096,7 +5254,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5104,14 +5262,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>33003</v>
+        <v>35098</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>68335</v>
+        <v>68226</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5120,14 +5278,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5140,16 +5298,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5157,14 +5311,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35098</v>
+        <v>24998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33296</v>
+        <v>23847</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5173,19 +5327,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5193,43 +5347,35 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5238,7 +5384,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5263,7 +5409,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35098</v>
+        <v>35099</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>68226</v>
@@ -5278,16 +5424,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5300,22 +5446,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24998</v>
+        <v>34795</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23847</v>
+        <v>60062</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5324,19 +5470,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5349,39 +5495,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48677</v>
+        <v>67680</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5394,7 +5544,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5402,14 +5552,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35099</v>
+        <v>34888</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>48940</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5418,19 +5568,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5443,22 +5593,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34795</v>
+        <v>34997</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60062</v>
+        <v>14634</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5467,19 +5617,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5492,22 +5642,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>32495</v>
+        <v>5000</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67680</v>
+        <v>41000</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5516,19 +5659,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5541,22 +5684,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34888</v>
+        <v>34795</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48940</v>
+        <v>60062</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5565,19 +5708,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5590,7 +5733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5598,35 +5741,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34997</v>
+        <v>33995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14634</v>
+        <v>50530</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5639,36 +5782,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>5000</v>
+        <v>31998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>41000</v>
+        <v>54169</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5681,43 +5831,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>60062</v>
+        <v>33892</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5725,39 +5868,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>50530</v>
+        <v>32492</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5766,7 +5906,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5774,48 +5914,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>54169</v>
+        <v>30792</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5823,36 +5960,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
-        <v>33892</v>
+        <v>34888</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5867,7 +6015,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
@@ -5882,7 +6030,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>32492</v>
+        <v>30992</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -5891,14 +6039,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5911,11 +6059,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5928,23 +6072,23 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>30792</v>
+        <v>32794</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5957,52 +6101,38 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>48940</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6010,11 +6140,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6027,7 +6153,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>30992</v>
+        <v>29992</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -6036,19 +6162,19 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -6058,131 +6184,8 @@
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>32794</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>16</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>17</v>
-      </c>
-      <c r="I27" t="n">
-        <v>18</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>29992</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>18</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M28"/>
+  <autoFilter ref="A1:M25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6208,9 +6211,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30500</v>
+        <v>32000</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>49170</v>
+        <v>69539</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>62599</v>
+        <v>67680</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,22 +613,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -648,10 +644,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -661,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -685,41 +681,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>55369</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,41 +717,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>34998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>68226</v>
+        <v>67017</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -777,138 +747,14 @@
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>18</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>32999</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>55369</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>37</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4970,7 +4816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5058,11 +4904,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5070,31 +4916,31 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>34990</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37000</v>
+        <v>48677</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5102,16 +4948,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5119,14 +4961,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>34998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47938</v>
+        <v>62599</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5135,19 +4977,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5155,23 +4997,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>27500</v>
+        <v>34998</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33173</v>
+        <v>68226</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5180,11 +5030,11 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>2026-08-22</t>
@@ -5192,7 +5042,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5205,7 +5055,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5213,14 +5063,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>30998</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67531</v>
+        <v>37000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5229,19 +5079,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5249,12 +5099,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5262,14 +5116,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35098</v>
+        <v>32495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>68226</v>
+        <v>47938</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5278,19 +5132,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5303,22 +5157,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>24998</v>
+        <v>27500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23847</v>
+        <v>33173</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5327,19 +5177,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5352,27 +5202,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48677</v>
+        <v>67531</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -5384,7 +5238,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5409,7 +5263,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35099</v>
+        <v>35098</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>68226</v>
@@ -5424,16 +5278,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5446,22 +5300,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34795</v>
+        <v>24998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60062</v>
+        <v>23847</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5470,19 +5324,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5495,43 +5349,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67680</v>
+        <v>48677</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5544,7 +5394,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5552,14 +5402,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34888</v>
+        <v>35099</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48940</v>
+        <v>68226</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5568,19 +5418,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5593,22 +5443,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34997</v>
+        <v>34795</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14634</v>
+        <v>60062</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5617,19 +5467,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5642,15 +5492,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>5000</v>
+        <v>32495</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41000</v>
+        <v>67680</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5659,19 +5516,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5684,22 +5541,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5708,19 +5565,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5733,7 +5590,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5741,35 +5598,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>33995</v>
+        <v>34997</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50530</v>
+        <v>14634</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5782,43 +5639,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>31998</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>54169</v>
+        <v>41000</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5831,36 +5681,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>33892</v>
+        <v>34795</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>60062</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5868,36 +5725,39 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>32492</v>
+        <v>33995</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5906,7 +5766,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5914,45 +5774,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>30792</v>
+        <v>31998</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5960,47 +5823,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>48940</v>
+        <v>33892</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6015,7 +5867,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -6030,7 +5882,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>30992</v>
+        <v>32492</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -6039,14 +5891,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6059,7 +5911,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6072,23 +5928,23 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>32794</v>
+        <v>30792</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6101,38 +5957,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>48940</v>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lefebvre Toyota</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6140,7 +6010,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6153,7 +6027,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>29992</v>
+        <v>30992</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -6162,30 +6036,153 @@
         </is>
       </c>
       <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>32794</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>18</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
+        <v>29992</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="I25" t="n">
-        <v>19</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6211,6 +6208,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32000</v>
+        <v>27500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>69539</v>
+        <v>55392</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,18 +564,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,7 +579,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +587,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>34998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67680</v>
+        <v>14334</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,18 +609,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33495</v>
+        <v>32000</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52500</v>
+        <v>59051</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,23 +657,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -681,28 +685,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>32999</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55369</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -717,44 +734,218 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>33495</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>52500</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>55369</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C9" t="n">
         <v>2024</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>34998</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>67017</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hondasoreltracy</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>38</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>39</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33998</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>56937</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4816,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4931,7 +5122,7 @@
         <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4953,22 +5144,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34998</v>
+        <v>30998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>62599</v>
+        <v>37000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -4977,19 +5168,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -4999,14 +5190,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35,099 → 35,098 → 34,998</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5014,14 +5205,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>68226</v>
+        <v>47938</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5030,19 +5221,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5055,7 +5246,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5063,14 +5254,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>30998</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37000</v>
+        <v>67531</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5079,19 +5270,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5099,16 +5290,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5116,14 +5303,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32495</v>
+        <v>35098</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>47938</v>
+        <v>68226</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5132,19 +5319,19 @@
         </is>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5157,18 +5344,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>27500</v>
+        <v>24998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33173</v>
+        <v>23847</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5177,19 +5368,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5202,34 +5393,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5238,7 +5425,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5263,7 +5450,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35098</v>
+        <v>35099</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>68226</v>
@@ -5278,16 +5465,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5300,22 +5487,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24998</v>
+        <v>34795</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23847</v>
+        <v>60062</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5324,19 +5511,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5349,39 +5536,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>34990</v>
+        <v>32495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48677</v>
+        <v>67680</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5394,7 +5585,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5402,14 +5593,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35099</v>
+        <v>34888</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>48940</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5418,19 +5609,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5443,22 +5634,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34795</v>
+        <v>34997</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60062</v>
+        <v>14634</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5467,19 +5658,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5492,22 +5683,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>32495</v>
+        <v>5000</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67680</v>
+        <v>41000</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5516,19 +5700,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5541,22 +5725,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34888</v>
+        <v>34795</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48940</v>
+        <v>60062</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5565,19 +5749,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5590,7 +5774,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5598,35 +5782,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34997</v>
+        <v>33995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14634</v>
+        <v>50530</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5639,36 +5823,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>5000</v>
+        <v>31998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>41000</v>
+        <v>54169</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5681,43 +5872,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>60062</v>
+        <v>33892</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5725,39 +5909,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>50530</v>
+        <v>32492</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5766,7 +5947,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5774,48 +5955,45 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>54169</v>
+        <v>30792</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5823,36 +6001,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
-        <v>33892</v>
+        <v>34888</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
         <v>19</v>
       </c>
-      <c r="I21" t="n">
-        <v>18</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5867,7 +6056,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
@@ -5882,7 +6071,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>32492</v>
+        <v>30992</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -5891,14 +6080,14 @@
         </is>
       </c>
       <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>19</v>
       </c>
-      <c r="I22" t="n">
-        <v>18</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5911,11 +6100,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5928,23 +6113,23 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="n">
-        <v>30792</v>
+        <v>32794</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>19</v>
       </c>
-      <c r="I23" t="n">
-        <v>18</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5957,52 +6142,38 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>48940</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -6010,11 +6181,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6027,7 +6194,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>30992</v>
+        <v>29992</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -6036,19 +6203,19 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -6058,131 +6225,8 @@
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>32794</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>18</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>17</v>
-      </c>
-      <c r="I27" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>29992</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M28"/>
+  <autoFilter ref="A1:M25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6208,9 +6252,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27500</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>55392</v>
+        <v>2448</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,14 +564,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34998</v>
+        <v>27500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14334</v>
+        <v>55392</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,18 +617,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32000</v>
+        <v>34997</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59051</v>
+        <v>10992</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,18 +666,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,7 +681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -693,14 +689,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34998</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>28950</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -715,18 +711,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -759,16 +759,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,22 +783,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34998</v>
+        <v>34995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>68226</v>
+        <v>60062</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -817,14 +817,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -832,28 +836,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>32999</v>
+        <v>33495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>55369</v>
+        <v>52500</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -868,28 +885,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>34998</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67017</v>
+        <v>68226</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -911,21 +941,21 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33998</v>
+        <v>32999</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>56937</v>
+        <v>55369</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -934,8 +964,44 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>40</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -946,6 +1012,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5007,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5107,31 +5174,31 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34990</v>
+        <v>32000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>48677</v>
+        <v>59051</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5139,27 +5206,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>30998</v>
+        <v>33998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>37000</v>
+        <v>56937</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5168,19 +5235,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5188,16 +5255,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5205,35 +5268,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>47938</v>
+        <v>48677</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5246,11 +5309,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5258,10 +5321,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67531</v>
+        <v>47938</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5270,19 +5333,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5295,22 +5358,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35098</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5319,14 +5382,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5344,7 +5407,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5352,14 +5415,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24998</v>
+        <v>35098</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23847</v>
+        <v>68226</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5368,19 +5431,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5393,34 +5456,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>34990</v>
+        <v>24998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48677</v>
+        <v>23847</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5438,27 +5505,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>35099</v>
+        <v>34990</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5469,12 +5532,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5487,22 +5550,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34795</v>
+        <v>35099</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60062</v>
+        <v>68226</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5511,19 +5574,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5563,7 +5626,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5612,7 +5675,7 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5634,43 +5697,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34997</v>
+        <v>5000</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14634</v>
+        <v>41000</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5683,36 +5739,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>5000</v>
+        <v>34795</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41000</v>
+        <v>60062</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5725,43 +5788,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34795</v>
+        <v>33995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60062</v>
+        <v>50530</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5774,7 +5837,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5782,30 +5845,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>33995</v>
+        <v>31998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50530</v>
+        <v>54169</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5823,43 +5886,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>54169</v>
+        <v>33892</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5867,7 +5923,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>33,992 → 33,892</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5880,7 +5940,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>33892</v>
+        <v>32492</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5892,7 +5952,7 @@
         <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5911,7 +5971,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>33,992 → 33,892</t>
+          <t>32,892 → 32,492</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5986,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>32492</v>
+        <v>30792</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -5938,7 +5998,7 @@
         <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5957,38 +6017,45 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>32,892 → 32,492</t>
+          <t>31,992 → 30,992 → 30,792</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>30792</v>
+        <v>34888</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>48940</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -6003,45 +6070,38 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>31,992 → 30,992 → 30,792</t>
+          <t>34,895 → 34,888</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>48940</v>
+        <v>30992</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6054,11 +6114,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6071,19 +6127,19 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>30992</v>
+        <v>32794</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -6102,131 +6158,8 @@
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" s="2" t="n">
-        <v>32794</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>19</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>17</v>
-      </c>
-      <c r="I24" t="n">
-        <v>21</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>29992</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6249,9 +6182,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>27500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2448</v>
+        <v>43004</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,18 +564,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,7 +579,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +587,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27500</v>
+        <v>34998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>55392</v>
+        <v>33650</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,14 +613,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34997</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10992</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,22 +681,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34998</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>28950</v>
+        <v>60062</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>35,099 → 35,098 → 34,998</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -759,16 +759,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,22 +783,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60062</v>
+        <v>68226</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -817,18 +817,14 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -836,41 +832,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33495</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52500</v>
+        <v>67017</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -885,41 +868,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>34998</v>
+        <v>35492</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>68226</v>
+        <v>63289</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -934,28 +904,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>32999</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>55369</v>
+        <v>2024</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -964,44 +928,8 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>40</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1012,7 +940,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5074,7 +5001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5162,11 +5089,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5174,10 +5101,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32000</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>59051</v>
+        <v>2448</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5186,19 +5113,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5208,7 +5135,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -5223,31 +5150,31 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>33998</v>
+        <v>32999</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56937</v>
+        <v>55369</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5260,7 +5187,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5268,35 +5195,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34990</v>
+        <v>34997</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>48677</v>
+        <v>10992</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5309,7 +5236,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5317,14 +5244,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32495</v>
+        <v>32000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>47938</v>
+        <v>59051</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5333,19 +5260,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5353,27 +5280,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>33998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67531</v>
+        <v>56937</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5382,19 +5309,19 @@
         </is>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5407,7 +5334,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5415,35 +5342,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5456,7 +5383,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5464,14 +5391,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24998</v>
+        <v>32495</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>23847</v>
+        <v>47938</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5480,19 +5407,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5505,27 +5432,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>48677</v>
+        <v>67531</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
@@ -5537,7 +5468,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5562,7 +5493,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35099</v>
+        <v>35098</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>68226</v>
@@ -5577,16 +5508,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5599,7 +5530,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5607,35 +5538,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32495</v>
+        <v>24998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67680</v>
+        <v>23847</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5648,43 +5579,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5697,36 +5624,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>5000</v>
+        <v>35099</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>41000</v>
+        <v>68226</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5739,43 +5673,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34795</v>
+        <v>32495</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5800,31 +5734,31 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>33995</v>
+        <v>34888</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>50530</v>
+        <v>48940</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5837,43 +5771,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>31998</v>
+        <v>5000</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54169</v>
+        <v>41000</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5886,36 +5813,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>33892</v>
+        <v>34795</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>60062</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5923,36 +5857,39 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>32492</v>
+        <v>33995</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5961,7 +5898,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5969,45 +5906,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>30792</v>
+        <v>31998</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -6015,47 +5955,36 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>48940</v>
+        <v>33892</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -6070,7 +5999,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>34,895 → 34,888</t>
+          <t>33,992 → 33,892</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6014,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="n">
-        <v>30992</v>
+        <v>32492</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -6094,14 +6023,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6114,7 +6043,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>32,892 → 32,492</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6127,39 +6060,180 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>32794</v>
+        <v>30792</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>19</v>
+      </c>
+      <c r="I22" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>31,992 → 30,992 → 30,792</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>34,895 → 34,888</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>30992</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>21</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>32794</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="I25" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M22"/>
+  <autoFilter ref="A1:M25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6182,6 +6256,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
         <v>27500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43004</v>
+        <v>62995</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +587,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>33650</v>
+        <v>67680</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -609,22 +609,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -644,10 +640,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,16 +653,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,52 +677,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60062</v>
+        <v>55369</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -734,41 +713,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>34998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67017</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,41 +749,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>68226</v>
+        <v>56937</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,28 +785,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34998</v>
+        <v>35492</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67017</v>
+        <v>63289</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -862,74 +815,8 @@
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>35492</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -938,8 +825,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5001,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5089,7 +4974,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5097,14 +4982,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>34995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2448</v>
+        <v>60062</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5113,19 +4998,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5135,46 +5020,50 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55369</v>
+        <v>33650</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5182,12 +5071,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5195,14 +5088,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34997</v>
+        <v>34998</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10992</v>
+        <v>68226</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5211,19 +5104,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5236,43 +5129,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>59051</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5280,27 +5163,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>33998</v>
+        <v>30998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>56937</v>
+        <v>2448</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5309,19 +5192,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5329,12 +5212,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5342,35 +5229,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34990</v>
+        <v>34997</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48677</v>
+        <v>10992</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5383,7 +5270,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5391,14 +5278,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32495</v>
+        <v>32000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47938</v>
+        <v>59051</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5407,19 +5294,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5427,48 +5314,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5481,7 +5372,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5489,14 +5380,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35098</v>
+        <v>32495</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>68226</v>
+        <v>47938</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5505,19 +5396,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5530,22 +5421,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>24998</v>
+        <v>34995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23847</v>
+        <v>67531</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5554,19 +5445,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5579,23 +5470,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -5606,12 +5501,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5624,7 +5519,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5632,14 +5527,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35099</v>
+        <v>24998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5648,19 +5543,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5673,43 +5568,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>32495</v>
+        <v>34990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67680</v>
+        <v>48677</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5722,7 +5613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5730,14 +5621,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34888</v>
+        <v>35099</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48940</v>
+        <v>68226</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5746,19 +5637,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5771,15 +5662,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>5000</v>
+        <v>32495</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41000</v>
+        <v>67680</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5788,19 +5686,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5813,22 +5711,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34795</v>
+        <v>34888</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>60062</v>
+        <v>48940</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5837,19 +5735,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5862,34 +5760,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>33995</v>
+        <v>5000</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>50530</v>
+        <v>41000</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5898,7 +5789,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5911,22 +5802,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>31998</v>
+        <v>34795</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>54169</v>
+        <v>60062</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -5935,19 +5826,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>17</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5960,27 +5851,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>33892</v>
+        <v>33995</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>50530</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5989,7 +5887,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -5997,45 +5895,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>33,992 → 33,892</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
-        <v>32492</v>
+        <v>31998</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>54169</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -6043,197 +5944,10 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>32,892 → 32,492</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" s="2" t="n">
-        <v>30792</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>31,992 → 30,992 → 30,792</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>48940</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>34,895 → 34,888</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>30992</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>21</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>32794</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6255,10 +5969,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27500</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>62995</v>
+        <v>17345</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,14 +564,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>27500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67680</v>
+        <v>62995</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -609,11 +613,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -628,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -636,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33495</v>
+        <v>32000</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52500</v>
+        <v>52234</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -653,23 +657,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -677,28 +685,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>32999</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55369</v>
+        <v>51952</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -713,28 +734,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67017</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -749,28 +783,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>33998</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56937</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -792,31 +839,139 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35492</v>
+        <v>32999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63289</v>
+        <v>55369</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>43</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33998</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>56937</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>35492</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>63289</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -825,6 +980,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4886,7 +5044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5001,7 +5159,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5054,7 +5212,7 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5107,7 +5265,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5146,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5168,22 +5326,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30998</v>
+        <v>34997</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2448</v>
+        <v>10992</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5192,14 +5350,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5212,16 +5370,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5229,35 +5383,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34997</v>
+        <v>34990</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10992</v>
+        <v>48677</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5270,22 +5424,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32000</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>59051</v>
+        <v>67531</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5294,19 +5448,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5314,16 +5468,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5331,35 +5481,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5372,7 +5522,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5380,14 +5530,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32495</v>
+        <v>24998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>47938</v>
+        <v>23847</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5396,19 +5546,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5421,34 +5571,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5457,7 +5603,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5482,7 +5628,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35098</v>
+        <v>35099</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>68226</v>
@@ -5497,16 +5643,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5519,7 +5665,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5527,35 +5673,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24998</v>
+        <v>32495</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23847</v>
+        <v>67680</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5568,39 +5714,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>34990</v>
+        <v>34888</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48677</v>
+        <v>48940</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5613,43 +5763,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>35099</v>
+        <v>5000</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>68226</v>
+        <v>41000</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5662,43 +5805,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32495</v>
+        <v>34795</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67680</v>
+        <v>60062</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5723,31 +5866,31 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34888</v>
+        <v>33995</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48940</v>
+        <v>50530</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Toyotamontlaurier</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5760,36 +5903,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>5000</v>
+        <v>31998</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41000</v>
+        <v>54169</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5799,155 +5949,8 @@
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>23</v>
-      </c>
-      <c r="I20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>54169</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>18</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5966,9 +5969,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>32000</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17345</v>
+        <v>41886</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27500</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>62995</v>
+        <v>51952</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32000</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52234</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -662,22 +662,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -697,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>51952</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -710,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,41 +730,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
+        <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>34998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>67017</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,41 +766,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2023</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>35492</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>63289</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -826,152 +796,8 @@
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>32999</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>55369</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>19</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>43</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>33998</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>56937</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>35492</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -979,10 +805,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5044,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5132,7 +4954,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5140,14 +4962,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34995</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60062</v>
+        <v>17345</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5156,19 +4978,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5178,50 +5000,46 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>34,795 → 34,995</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33650</v>
+        <v>55369</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5229,16 +5047,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5246,14 +5060,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34998</v>
+        <v>27500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>68226</v>
+        <v>62995</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5262,10 +5076,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5274,7 +5088,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5287,33 +5101,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>33998</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>56937</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5326,22 +5146,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34997</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10992</v>
+        <v>60062</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5350,19 +5170,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5370,12 +5190,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5383,35 +5207,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48677</v>
+        <v>33650</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5419,27 +5243,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>67531</v>
+        <v>68226</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5448,19 +5276,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5473,43 +5301,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>35098</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>68226</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5522,7 +5340,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5530,14 +5348,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24998</v>
+        <v>34997</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23847</v>
+        <v>10992</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5549,16 +5367,16 @@
         <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5571,13 +5389,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
         <v>34990</v>
       </c>
@@ -5587,23 +5409,23 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5616,22 +5438,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35099</v>
+        <v>34995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5640,19 +5462,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5665,7 +5487,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5673,35 +5495,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32495</v>
+        <v>35098</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67680</v>
+        <v>68226</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5726,10 +5548,10 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34888</v>
+        <v>24998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48940</v>
+        <v>23847</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5738,19 +5560,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5763,36 +5585,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>5000</v>
+        <v>34990</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>41000</v>
+        <v>48677</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5805,22 +5630,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34795</v>
+        <v>35099</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60062</v>
+        <v>68226</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5829,19 +5654,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5854,7 +5679,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5862,35 +5687,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>33995</v>
+        <v>32495</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50530</v>
+        <v>67680</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5903,7 +5728,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5911,14 +5736,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>31998</v>
+        <v>34888</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>54169</v>
+        <v>48940</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5927,30 +5752,219 @@
         </is>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34795</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>60062</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>50530</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Otogo.ca, Toyotamontlaurier</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>23</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>31998</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>54169</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5969,6 +5983,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32000</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>41886</v>
+        <v>37000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>32000</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>51952</v>
+        <v>41886</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,14 +617,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -666,7 +670,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -715,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -751,7 +755,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -787,7 +791,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -4954,22 +4958,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17345</v>
+        <v>51952</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -4978,19 +4982,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -4998,11 +5002,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5030,7 +5030,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>27500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>37000</v>
+        <v>9</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,18 +564,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -598,7 +594,7 @@
         <v>32000</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>41886</v>
+        <v>30810</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,7 +613,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -644,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34997</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>27791</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,11 +662,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -697,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -710,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,28 +730,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34998</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67017</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -777,31 +786,103 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35492</v>
+        <v>31998</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>63289</v>
+        <v>56361</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>46</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>35492</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>63289</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -809,6 +890,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4870,7 +4953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4958,22 +5041,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>51952</v>
+        <v>37000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -4982,19 +5065,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5002,44 +5085,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2023</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>32999</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55369</v>
+        <v>51952</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5052,38 +5143,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>27500</v>
+        <v>32999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62995</v>
+        <v>55369</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5124,7 +5211,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5173,7 +5260,7 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5226,7 +5313,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5279,7 +5366,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5318,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5340,7 +5427,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5348,35 +5435,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>34997</v>
+        <v>34990</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10992</v>
+        <v>48677</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5389,43 +5476,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48677</v>
+        <v>67531</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5438,22 +5525,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34995</v>
+        <v>35098</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>67531</v>
+        <v>68226</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5462,14 +5549,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5487,7 +5574,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5495,14 +5582,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35098</v>
+        <v>24998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5511,19 +5598,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5536,38 +5623,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>24998</v>
+        <v>34990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23847</v>
+        <v>48677</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5585,39 +5668,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>34990</v>
+        <v>35099</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5630,7 +5717,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5638,35 +5725,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35099</v>
+        <v>32495</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>68226</v>
+        <v>67680</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5679,7 +5766,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5687,35 +5774,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32495</v>
+        <v>34888</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>67680</v>
+        <v>48940</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5728,43 +5815,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+          <t>Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>34888</v>
+        <v>5000</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>48940</v>
+        <v>41000</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5777,36 +5857,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>5000</v>
+        <v>34795</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>41000</v>
+        <v>60062</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5816,155 +5903,8 @@
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>50530</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Toyotamontlaurier</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>23</v>
-      </c>
-      <c r="I21" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>54169</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M22"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5984,9 +5924,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27500</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9</v>
+        <v>17345</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,14 +564,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -579,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -587,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32000</v>
+        <v>34997</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>30810</v>
+        <v>51071</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -613,18 +617,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34997</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27791</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,22 +681,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>60062</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -711,18 +711,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -764,7 +768,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -800,7 +804,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -815,28 +819,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2024</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>34998</v>
+        <v>34995</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67017</v>
+        <v>67531</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -858,31 +875,103 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>35492</v>
+        <v>32488</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>63289</v>
+        <v>63212</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>47</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>35492</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>63289</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -892,6 +981,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4953,7 +5044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5041,11 +5132,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5053,10 +5144,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>32000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37000</v>
+        <v>30810</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5072,12 +5163,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5087,7 +5178,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
         </is>
       </c>
     </row>
@@ -5109,28 +5200,28 @@
         <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>51952</v>
+        <v>67680</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5143,39 +5234,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2023</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>32999</v>
+        <v>27500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>55369</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5188,18 +5283,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>33998</v>
+        <v>32495</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56937</v>
+        <v>51952</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5208,19 +5307,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5233,43 +5332,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60062</v>
+        <v>55369</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5277,31 +5372,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33650</v>
+        <v>56937</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5310,19 +5397,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5330,11 +5417,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5354,7 +5437,7 @@
         <v>34998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68226</v>
+        <v>33650</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5363,14 +5446,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5383,33 +5466,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>68226</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5427,43 +5524,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>48677</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5476,43 +5563,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5525,22 +5612,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35098</v>
+        <v>34995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5549,14 +5636,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5574,7 +5661,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5582,14 +5669,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24998</v>
+        <v>35098</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23847</v>
+        <v>68226</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5598,19 +5685,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5623,34 +5710,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>34990</v>
+        <v>24998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48677</v>
+        <v>23847</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5668,27 +5759,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>35099</v>
+        <v>34990</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -5699,12 +5786,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5717,7 +5804,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5725,35 +5812,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32495</v>
+        <v>35099</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67680</v>
+        <v>68226</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5793,7 +5880,7 @@
         <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5835,7 +5922,7 @@
         <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5854,57 +5941,8 @@
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>34795</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>60062</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5923,7 +5961,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>27200</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17345</v>
+        <v>68937</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>27,500 → 27,200</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34997</v>
+        <v>31500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>51071</v>
+        <v>39577</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,14 +617,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +636,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +644,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>33897</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>58016</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,12 +661,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -673,7 +677,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -681,22 +689,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -711,22 +719,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -768,7 +772,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -804,7 +808,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -819,7 +823,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -827,26 +831,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34995</v>
+        <v>35299</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67531</v>
+        <v>53475</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>AutoTrader</t>
@@ -868,28 +864,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32488</v>
+        <v>34998</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>63212</v>
+        <v>67017</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -904,28 +900,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34998</v>
+        <v>35492</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>67017</v>
+        <v>63289</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -934,44 +930,8 @@
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>35492</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -982,7 +942,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5044,7 +5003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5132,11 +5091,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5144,10 +5103,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32000</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30810</v>
+        <v>17345</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5156,19 +5115,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5178,50 +5137,50 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67680</v>
+        <v>60062</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5229,12 +5188,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5242,35 +5205,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>27500</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9</v>
+        <v>67680</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5283,11 +5246,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5295,10 +5258,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51952</v>
+        <v>67531</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5307,19 +5270,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5340,31 +5303,31 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>32999</v>
+        <v>32488</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55369</v>
+        <v>63212</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5377,18 +5340,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>33998</v>
+        <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56937</v>
+        <v>51952</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5397,19 +5364,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5422,43 +5389,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33650</v>
+        <v>55369</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5466,31 +5429,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68226</v>
+        <v>56937</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5499,19 +5454,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5524,46 +5479,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33650</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5571,35 +5540,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5612,43 +5581,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2024</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>67531</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5661,7 +5620,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5669,35 +5628,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5710,22 +5669,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24998</v>
+        <v>34995</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23847</v>
+        <v>67531</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5734,19 +5693,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5759,23 +5718,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -5786,12 +5749,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5804,7 +5767,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5812,14 +5775,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35099</v>
+        <v>24998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5828,19 +5791,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
         <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5853,43 +5816,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5902,36 +5861,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>5000</v>
+        <v>35099</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41000</v>
+        <v>68226</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5941,8 +5907,57 @@
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5961,6 +5976,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27200</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>68937</v>
+        <v>53754</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27,500 → 27,200</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31500</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>39577</v>
+        <v>67680</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,27 +608,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -636,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33897</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58016</v>
+        <v>60062</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -670,18 +666,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -701,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -714,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -738,11 +730,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -750,10 +742,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>34995</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>67531</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -763,16 +755,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -787,28 +779,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>31998</v>
+        <v>35299</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56361</v>
+        <v>53475</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -823,33 +820,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2024</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>35299</v>
+        <v>34998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53475</v>
+        <v>67017</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -864,74 +856,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34998</v>
+        <v>34992</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67017</v>
+        <v>63289</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>35492</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35,492 → 34,992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -941,7 +901,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5003,7 +4962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5091,11 +5050,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5103,10 +5062,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>31500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17345</v>
+        <v>39577</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5122,12 +5081,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5137,29 +5096,29 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34995</v>
+        <v>33897</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60062</v>
+        <v>58016</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5168,19 +5127,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5190,7 +5149,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34,795 → 34,995</t>
+          <t>34,997 → 33,897</t>
         </is>
       </c>
     </row>
@@ -5217,23 +5176,23 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5246,22 +5205,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>27200</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67531</v>
+        <v>68937</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5270,19 +5229,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5290,7 +5249,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5303,31 +5266,31 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>32488</v>
+        <v>31998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63212</v>
+        <v>56361</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5340,22 +5303,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>51952</v>
+        <v>60062</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5364,19 +5327,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5384,7 +5347,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5397,31 +5364,31 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>32999</v>
+        <v>32488</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55369</v>
+        <v>63212</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5434,18 +5401,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>33998</v>
+        <v>32495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>56937</v>
+        <v>51952</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5454,19 +5425,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5479,43 +5450,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33650</v>
+        <v>55369</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5523,31 +5490,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>68226</v>
+        <v>56937</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5556,19 +5515,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5581,46 +5540,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>33650</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5628,35 +5601,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5669,43 +5642,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>67531</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5718,7 +5681,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5726,35 +5689,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5767,22 +5730,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24998</v>
+        <v>34995</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23847</v>
+        <v>67531</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5791,19 +5754,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5816,23 +5779,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -5843,12 +5810,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5861,7 +5828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5869,14 +5836,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>35099</v>
+        <v>24998</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5885,19 +5852,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
         <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5910,54 +5877,148 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="n">
-        <v>34888</v>
+        <v>34990</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>48940</v>
+        <v>48677</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>35099</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>AutoTrader</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>16</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>34888</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>48940</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I21" t="n">
+        <v>19</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5977,6 +6038,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>27200</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>53754</v>
+        <v>19323</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>27,500 → 27,200</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>33897</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67680</v>
+        <v>32954</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -624,7 +624,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,22 +636,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60062</v>
+        <v>19732</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,7 +670,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -693,10 +697,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,11 +734,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -742,10 +746,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34995</v>
+        <v>33495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67531</v>
+        <v>52500</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -755,16 +759,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,7 +783,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -787,25 +791,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53475</v>
+        <v>67531</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -841,7 +853,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -877,7 +889,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -5050,11 +5062,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5062,10 +5074,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>31500</v>
+        <v>30998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>39577</v>
+        <v>53754</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5074,19 +5086,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5096,14 +5108,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5111,35 +5123,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>33897</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58016</v>
+        <v>67680</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5147,52 +5159,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>35299</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67680</v>
+        <v>53475</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5205,22 +5213,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>27200</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>68937</v>
+        <v>60062</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5229,19 +5237,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5249,43 +5257,43 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>31998</v>
+        <v>31500</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>56361</v>
+        <v>39577</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5298,48 +5306,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>31998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60062</v>
+        <v>56361</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5347,97 +5355,97 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>32488</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>63212</v>
+        <v>60062</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>32495</v>
+        <v>32488</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>51952</v>
+        <v>63212</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5473,7 +5481,7 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5518,7 +5526,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5567,7 +5575,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5620,7 +5628,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5659,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5708,7 +5716,7 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5757,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5806,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5855,7 +5863,7 @@
         <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5900,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5949,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5998,7 +6006,7 @@
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33897</v>
+        <v>31500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32954</v>
+        <v>39577</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19732</v>
+        <v>51405</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,22 +734,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33495</v>
+        <v>34995</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52500</v>
+        <v>60062</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -759,16 +759,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34995</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67531</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -808,16 +808,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,28 +832,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34998</v>
+        <v>31998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67017</v>
+        <v>56361</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -868,42 +868,127 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>67531</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>51</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>2023</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>63289</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -913,6 +998,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4974,7 +5061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5062,22 +5149,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30998</v>
+        <v>33897</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53754</v>
+        <v>32954</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5086,19 +5173,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5108,45 +5195,45 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>34,997 → 33,897</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>30998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67680</v>
+        <v>53754</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5159,43 +5246,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35299</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53475</v>
+        <v>67680</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5213,7 +5304,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5221,14 +5312,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>35299</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60062</v>
+        <v>53475</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5237,14 +5328,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5262,22 +5353,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>31500</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39577</v>
+        <v>60062</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5286,19 +5377,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5308,7 +5399,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
@@ -5323,31 +5414,31 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>31998</v>
+        <v>32488</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56361</v>
+        <v>63212</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5360,43 +5451,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60062</v>
+        <v>55369</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5404,11 +5491,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5421,31 +5504,31 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>32488</v>
+        <v>33998</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>63212</v>
+        <v>56937</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5458,39 +5541,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>55369</v>
+        <v>33650</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5498,23 +5585,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>33998</v>
+        <v>34998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>56937</v>
+        <v>68226</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5523,19 +5618,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5548,38 +5643,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>33650</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>9</v>
       </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5592,16 +5677,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5609,35 +5690,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34998</v>
+        <v>34990</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5650,33 +5731,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>67531</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5689,7 +5780,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5697,35 +5788,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5738,22 +5829,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34995</v>
+        <v>24998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67531</v>
+        <v>23847</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5762,19 +5853,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5787,43 +5878,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5836,7 +5923,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5844,14 +5931,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>24998</v>
+        <v>35099</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>23847</v>
+        <v>68226</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -5860,19 +5947,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5885,39 +5972,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2023</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>34990</v>
+        <v>34888</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>48677</v>
+        <v>48940</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -5927,106 +6018,8 @@
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>35099</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>68226</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>17</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>34888</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>48940</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6046,8 +6039,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27200</v>
+        <v>31500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>19323</v>
+        <v>52234</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27,500 → 27,200</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31500</v>
+        <v>32495</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>39577</v>
+        <v>67680</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,27 +608,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -636,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>51405</v>
+        <v>60062</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -670,7 +666,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -697,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -710,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,41 +730,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34995</v>
+        <v>31998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60062</v>
+        <v>56361</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,11 +766,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -795,10 +778,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>34995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>67531</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -808,16 +791,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,28 +815,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>31998</v>
+        <v>35299</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56361</v>
+        <v>53475</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -868,41 +856,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2024</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67531</v>
+        <v>67017</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -917,78 +892,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34998</v>
+        <v>34992</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>67017</v>
+        <v>63289</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -999,7 +938,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5149,7 +5087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5157,35 +5095,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>33897</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32954</v>
+        <v>67680</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5193,31 +5131,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>53754</v>
+        <v>51405</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5226,19 +5160,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5246,16 +5180,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5263,35 +5193,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>27200</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67680</v>
+        <v>19323</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5299,27 +5229,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>35299</v>
+        <v>33897</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>53475</v>
+        <v>32954</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5328,19 +5262,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5348,12 +5282,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5361,14 +5299,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>30998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60062</v>
+        <v>53754</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5377,19 +5315,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5399,54 +5337,62 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>34,795 → 34,995</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>32488</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>63212</v>
+        <v>60062</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5459,31 +5405,31 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>32999</v>
+        <v>32488</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55369</v>
+        <v>63212</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5504,26 +5450,26 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>33998</v>
+        <v>32999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>56937</v>
+        <v>55369</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5541,22 +5487,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33650</v>
+        <v>56937</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5565,19 +5507,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5585,11 +5527,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5609,7 +5547,7 @@
         <v>34998</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>68226</v>
+        <v>33650</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -5618,14 +5556,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5638,33 +5576,47 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>68226</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5682,43 +5634,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>48677</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5731,43 +5673,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34995</v>
+        <v>34990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>67531</v>
+        <v>48677</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5780,22 +5722,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35098</v>
+        <v>34995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>68226</v>
+        <v>67531</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5804,14 +5746,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5829,7 +5771,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5837,14 +5779,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24998</v>
+        <v>35098</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23847</v>
+        <v>68226</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -5853,19 +5795,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>17</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5878,34 +5820,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2023</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="n">
-        <v>34990</v>
+        <v>24998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48677</v>
+        <v>23847</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5923,27 +5869,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>35099</v>
+        <v>34990</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -5954,12 +5896,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5972,7 +5914,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5980,14 +5922,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34888</v>
+        <v>35099</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>48940</v>
+        <v>68226</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -5996,19 +5938,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31500</v>
+        <v>27200</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>52234</v>
+        <v>19323</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+          <t>27,500 → 27,200</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32495</v>
+        <v>31500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67680</v>
+        <v>39577</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,23 +608,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,22 +636,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>60062</v>
+        <v>51405</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -666,7 +670,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,11 +685,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -693,10 +697,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>44246</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -711,11 +715,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,28 +734,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>31998</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56361</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -766,7 +783,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -774,14 +791,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>34995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67531</v>
+        <v>60062</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -800,7 +817,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -815,33 +832,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35299</v>
+        <v>33495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53475</v>
+        <v>52500</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -856,28 +881,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34998</v>
+        <v>31998</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67017</v>
+        <v>56361</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -892,42 +917,168 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>67531</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>35299</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>53475</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>67017</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hondasoreltracy</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>53</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>2023</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>63289</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>11</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K13" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -938,6 +1089,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4999,7 +5153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5107,23 +5261,23 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5136,7 +5290,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5144,14 +5298,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>33897</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>51405</v>
+        <v>32954</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5160,19 +5314,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5180,16 +5334,20 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5197,10 +5355,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>27200</v>
+        <v>30998</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19323</v>
+        <v>53754</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5209,19 +5367,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5231,29 +5389,29 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27,500 → 27,200</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33897</v>
+        <v>34995</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32954</v>
+        <v>60062</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5262,19 +5420,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5284,50 +5442,46 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>30998</v>
+        <v>32488</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>53754</v>
+        <v>63212</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5335,52 +5489,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60062</v>
+        <v>55369</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5388,11 +5534,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5405,31 +5547,31 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>32488</v>
+        <v>33998</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>63212</v>
+        <v>56937</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5442,39 +5584,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55369</v>
+        <v>33650</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5482,23 +5628,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>33998</v>
+        <v>34998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56937</v>
+        <v>68226</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5507,19 +5661,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5532,38 +5686,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>33650</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5576,16 +5720,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5593,35 +5733,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34998</v>
+        <v>34990</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5634,33 +5774,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2024</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34995</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>67531</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5673,7 +5823,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5681,35 +5831,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>18</v>
       </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5722,22 +5872,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34995</v>
+        <v>24998</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67531</v>
+        <v>23847</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5746,19 +5896,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5771,43 +5921,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5820,7 +5966,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5828,14 +5974,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24998</v>
+        <v>35099</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23847</v>
+        <v>68226</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5844,19 +5990,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5866,102 +6012,8 @@
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>35099</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>68226</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5979,8 +6031,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -636,11 +636,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34992</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>51405</v>
+        <v>44246</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -661,16 +661,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -685,11 +685,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34992</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44246</v>
+        <v>64792</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -710,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,22 +783,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34995</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60062</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -808,16 +808,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,41 +832,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33495</v>
+        <v>31998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52500</v>
+        <v>56361</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -881,24 +868,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2024</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31998</v>
+        <v>34995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>56361</v>
+        <v>67531</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -917,41 +917,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2024</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>67531</v>
+        <v>67017</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -966,119 +953,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>35299</v>
+        <v>34992</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>53475</v>
+        <v>63289</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>53</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1090,8 +1000,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5153,7 +5061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5241,43 +5149,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32495</v>
+        <v>35299</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67680</v>
+        <v>53475</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5290,22 +5198,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>33897</v>
+        <v>34995</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32954</v>
+        <v>60062</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -5314,19 +5222,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5334,52 +5242,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>30998</v>
+        <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53754</v>
+        <v>67680</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5387,31 +5291,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34995</v>
+        <v>33897</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>60062</v>
+        <v>32954</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5420,19 +5320,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5442,46 +5342,50 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34,795 → 34,995</t>
+          <t>34,997 → 33,897</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>32488</v>
+        <v>30998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63212</v>
+        <v>53754</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5489,44 +5393,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>32999</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55369</v>
+        <v>60062</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5534,7 +5446,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5547,31 +5463,31 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="n">
-        <v>33998</v>
+        <v>32488</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>56937</v>
+        <v>63212</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5584,43 +5500,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2023</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33650</v>
+        <v>55369</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5628,31 +5540,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2023</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>68226</v>
+        <v>56937</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5661,19 +5565,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5686,46 +5590,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>33650</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5733,35 +5651,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5774,43 +5692,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2024</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>67531</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5823,7 +5731,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5831,35 +5739,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5872,22 +5780,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24998</v>
+        <v>34995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23847</v>
+        <v>67531</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5896,19 +5804,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5921,23 +5829,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -5948,12 +5860,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5966,7 +5878,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5974,14 +5886,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35099</v>
+        <v>24998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5990,30 +5902,124 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>35099</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6031,6 +6037,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27200</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>19323</v>
+        <v>32216</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27,500 → 27,200</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,22 +583,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31500</v>
+        <v>34992</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>39577</v>
+        <v>44246</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,27 +608,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -636,22 +632,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34992</v>
+        <v>33907</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>44246</v>
+        <v>46771</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -661,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -700,7 +696,7 @@
         <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64792</v>
+        <v>67680</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -710,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,22 +730,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>60062</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -764,11 +760,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -817,7 +813,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -853,7 +849,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -868,11 +864,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -880,10 +876,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34995</v>
+        <v>33995</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67531</v>
+        <v>69400</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -893,16 +889,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -938,7 +934,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -974,7 +970,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -5061,7 +5057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5149,22 +5145,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35299</v>
+        <v>31500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53475</v>
+        <v>39577</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -5173,19 +5169,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5193,48 +5189,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60062</v>
+        <v>67680</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5262,28 +5262,28 @@
         <v>32495</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67680</v>
+        <v>64792</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5304,14 +5304,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33897</v>
+        <v>27200</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32954</v>
+        <v>19323</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5320,19 +5320,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>27,500 → 27,200</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30998</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>53754</v>
+        <v>67531</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5373,19 +5373,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5393,16 +5393,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5410,14 +5406,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>35299</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60062</v>
+        <v>53475</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5426,19 +5422,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5446,48 +5442,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2023</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>32488</v>
+        <v>33897</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>63212</v>
+        <v>32954</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5495,44 +5491,52 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>32999</v>
+        <v>34995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55369</v>
+        <v>60062</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5540,7 +5544,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5553,31 +5561,31 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>33998</v>
+        <v>32488</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>56937</v>
+        <v>63212</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5590,43 +5598,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33650</v>
+        <v>55369</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5634,31 +5638,23 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34998</v>
+        <v>33998</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>68226</v>
+        <v>56937</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5667,19 +5663,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5692,46 +5688,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>33650</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5739,35 +5749,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5780,43 +5790,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>67531</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5837,35 +5837,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35098</v>
+        <v>34990</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5878,22 +5878,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24998</v>
+        <v>34995</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23847</v>
+        <v>67531</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5902,19 +5902,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5927,23 +5927,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2023</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>34990</v>
+        <v>35098</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>48677</v>
+        <v>68226</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5972,7 +5976,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5980,14 +5984,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>35099</v>
+        <v>24998</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>68226</v>
+        <v>23847</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -5996,19 +6000,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
         <v>21</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -6018,8 +6022,53 @@
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Repentigny Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6039,6 +6088,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,14 +640,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33907</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46771</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67680</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -711,11 +711,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,41 +730,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
+        <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34995</v>
+        <v>31998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60062</v>
+        <v>56361</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -791,10 +778,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>33995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>69400</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -813,7 +800,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -835,156 +822,35 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>31998</v>
+        <v>34992</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56361</v>
+        <v>63289</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>69400</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>67017</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hondasoreltracy</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -993,9 +859,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5057,7 +4920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5145,43 +5008,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>31500</v>
+        <v>34998</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>39577</v>
+        <v>67017</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5189,52 +5048,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67680</v>
+        <v>60062</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5247,7 +5102,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5255,14 +5110,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32495</v>
+        <v>33907</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>64792</v>
+        <v>46771</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5271,19 +5126,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5308,10 +5163,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>27200</v>
+        <v>31500</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19323</v>
+        <v>39577</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5320,14 +5175,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5342,18 +5197,18 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27,500 → 27,200</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5361,26 +5216,26 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34995</v>
+        <v>32495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67531</v>
+        <v>67680</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5398,22 +5253,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35299</v>
+        <v>32495</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53475</v>
+        <v>64792</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5422,19 +5277,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5447,7 +5302,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5455,14 +5310,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33897</v>
+        <v>27200</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32954</v>
+        <v>19323</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5471,19 +5326,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5493,14 +5348,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>27,500 → 27,200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5508,14 +5363,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
         <v>34995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60062</v>
+        <v>67531</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5524,19 +5379,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5544,48 +5399,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>32488</v>
+        <v>35299</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>63212</v>
+        <v>53475</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5598,39 +5453,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>32999</v>
+        <v>33897</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>55369</v>
+        <v>32954</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5638,23 +5497,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>33998</v>
+        <v>34995</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>56937</v>
+        <v>60062</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5663,19 +5530,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5683,48 +5550,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>34998</v>
+        <v>32488</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>33650</v>
+        <v>63212</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5732,52 +5599,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>34998</v>
+        <v>32999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68226</v>
+        <v>55369</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5790,33 +5649,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>33998</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>56937</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5829,7 +5694,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5837,35 +5702,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>34990</v>
+        <v>34998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48677</v>
+        <v>33650</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5873,27 +5738,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT S-AWC</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>67531</v>
+        <v>68226</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -5902,19 +5771,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5927,43 +5796,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>35098</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>68226</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -5988,31 +5847,31 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>24998</v>
+        <v>34990</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>23847</v>
+        <v>48677</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -6025,27 +5884,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>34990</v>
+        <v>34995</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>48677</v>
+        <v>67531</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>21</v>
@@ -6057,7 +5920,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -6067,8 +5930,57 @@
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>35098</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>21</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6089,6 +6001,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
